--- a/1. Database Design/Java24 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java24 QuyenPhan Database Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF59DF54-F47F-440C-9C07-2903683C8A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AEBE31-D563-40CB-BB8F-A3EB2C3383D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="30045" windowHeight="20865" tabRatio="433" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21240" tabRatio="433" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,21 @@
     <sheet name="B3. Cơ sở dữ liệu vật lý" sheetId="3" r:id="rId3"/>
     <sheet name="B4. Database" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -933,6 +944,33 @@
         </r>
       </text>
     </comment>
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{C85C52E0-BD99-4804-9013-29D3508E31B4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Tiền mặt
+Thẻ ghị nợ
+Thẻ tín dụng
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="T7" authorId="0" shapeId="0" xr:uid="{6034391E-32E8-4DFA-8180-FC640051CA39}">
       <text>
         <r>
@@ -1141,6 +1179,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="T9" authorId="0" shapeId="0" xr:uid="{AAB3FCEA-512C-46B0-8BD2-07FC98591B5F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+DATE</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K10" authorId="0" shapeId="0" xr:uid="{18BB5900-BA99-40D2-8520-1D4ACDFD2899}">
       <text>
         <r>
@@ -1238,7 +1300,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="H56" authorId="0" shapeId="0" xr:uid="{8F332342-97CA-40D7-90EF-C0D4C39BA1FC}">
+    <comment ref="W12" authorId="0" shapeId="0" xr:uid="{66B66B77-F549-45C3-BA25-2DDE30CD85A3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Nhân viên thanh toán tiền thuế này</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H57" authorId="0" shapeId="0" xr:uid="{8F332342-97CA-40D7-90EF-C0D4C39BA1FC}">
       <text>
         <r>
           <rPr>
@@ -1262,7 +1348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H75" authorId="0" shapeId="0" xr:uid="{94511645-BFD9-4196-A589-4CE79279B2A4}">
+    <comment ref="H76" authorId="0" shapeId="0" xr:uid="{94511645-BFD9-4196-A589-4CE79279B2A4}">
       <text>
         <r>
           <rPr>
@@ -1292,7 +1378,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="383">
   <si>
     <t>MatHang</t>
   </si>
@@ -2652,9 +2738,6 @@
     <t>C21_EMPLOYEE_ID</t>
   </si>
   <si>
-    <t>C21_ROLE</t>
-  </si>
-  <si>
     <t>T22_TAX</t>
   </si>
   <si>
@@ -2682,33 +2765,12 @@
     <t>C23_CART_ID</t>
   </si>
   <si>
-    <t>T23_SHOPPING_CART</t>
-  </si>
-  <si>
     <t>C23_CUSTOMER_ID</t>
   </si>
   <si>
     <t>C23_DATE_CREATED</t>
   </si>
   <si>
-    <t>C23_ITEM_ID</t>
-  </si>
-  <si>
-    <t>C23_AMOUNT</t>
-  </si>
-  <si>
-    <t>C23_DATE_ADDING</t>
-  </si>
-  <si>
-    <t>C23_DATE_REMOVING</t>
-  </si>
-  <si>
-    <t>C24_CUSTOMER_ID</t>
-  </si>
-  <si>
-    <t>T24_CART_LATER_ON</t>
-  </si>
-  <si>
     <t>C24_ITEM_ID</t>
   </si>
   <si>
@@ -2716,13 +2778,88 @@
   </si>
   <si>
     <t>C22_TAX_PAYER_ID</t>
+  </si>
+  <si>
+    <t>Sau khi thiết kế cơ sở dữ liệu xong (logic, tài liệu)</t>
+  </si>
+  <si>
+    <t>Làm sao để đưa cơ sở dữ liệu đó vào thực tế sử dụng</t>
+  </si>
+  <si>
+    <t>2. Sử dụng database connection(backend framework) cấu hình, code trong phía backend để tạo table, column, constraints</t>
+  </si>
+  <si>
+    <t>1. Sử dụng SQL DDL tạo structure cho từng table, colum, constraints</t>
+  </si>
+  <si>
+    <t>3. Sử dụng sql editor, tạo diagram cho csdl, chuyển diagram sang sql ddl code, chạy sql ddl code để tạo csdl</t>
+  </si>
+  <si>
+    <t>- muốn tạo csdl phải chạy, deploy app</t>
+  </si>
+  <si>
+    <t>- khách hàng nắm business, không nắm code, phải mở code ra mới xem hiểu được</t>
+  </si>
+  <si>
+    <t>- hỗ trợ mức cơ bản, ko thể sử dụng hết các tính năng(mới) trong sql</t>
+  </si>
+  <si>
+    <t>- liên quan đến code thì mình nên dùng thao tác về dữ liệu(DML)</t>
+  </si>
+  <si>
+    <t>- ban đầu nhanh</t>
+  </si>
+  <si>
+    <t>- lưu code tạo csdl lại</t>
+  </si>
+  <si>
+    <t>- cần thay đổi gì thì phải chỉnh sửa diagram rồi generate lại từ đầu, mất dữ liệu …</t>
+  </si>
+  <si>
+    <t>- chỉ hỗ trợ mức đủ dùng</t>
+  </si>
+  <si>
+    <t>- tạo patches để chứa sql ddl script cho từng version</t>
+  </si>
+  <si>
+    <t>- quản lý được sql script cho từng version cho devs trong team</t>
+  </si>
+  <si>
+    <t>- liquibase</t>
+  </si>
+  <si>
+    <t>C21_ROLE_ID</t>
+  </si>
+  <si>
+    <t>T24_SHOPPING_CART</t>
+  </si>
+  <si>
+    <t>C24_CART_ID</t>
+  </si>
+  <si>
+    <t>C24_DATE_ADDING</t>
+  </si>
+  <si>
+    <t>C24_DATE_REMOVING</t>
+  </si>
+  <si>
+    <t>T25_CART_LATER_ON</t>
+  </si>
+  <si>
+    <t>C25_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C25_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C25_AMOUNT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2865,6 +3002,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -2976,7 +3126,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3116,13 +3266,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6355,7 +6508,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FF386C-4E85-4194-9348-4CECDAC92CFA}">
-  <dimension ref="A1:Z221"/>
+  <dimension ref="A1:Z222"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
@@ -6376,7 +6529,8 @@
     <col min="21" max="22" width="22.7109375" style="1" customWidth="1"/>
     <col min="23" max="23" width="28.85546875" style="1" customWidth="1"/>
     <col min="24" max="25" width="25" style="1" customWidth="1"/>
-    <col min="26" max="51" width="22.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="25.7109375" style="1" customWidth="1"/>
+    <col min="27" max="51" width="22.7109375" style="1" customWidth="1"/>
     <col min="52" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -6406,9 +6560,7 @@
       </c>
       <c r="G3" s="45"/>
       <c r="H3" s="46"/>
-      <c r="U3" s="4" t="s">
-        <v>143</v>
-      </c>
+      <c r="U3" s="4"/>
       <c r="X3" s="1" t="s">
         <v>141</v>
       </c>
@@ -6435,88 +6587,86 @@
       <c r="O4" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="U4" s="4"/>
       <c r="X4" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="5" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="48" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="48" t="s">
         <v>275</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="48" t="s">
         <v>300</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="48" t="s">
         <v>282</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="48" t="s">
         <v>290</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="48" t="s">
         <v>322</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="48" t="s">
         <v>326</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="T5" s="48" t="s">
         <v>332</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="V5" s="48" t="s">
         <v>342</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6584,16 +6734,16 @@
         <v>343</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Y6" s="41" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="Z6" s="41" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6618,7 +6768,7 @@
       <c r="H7" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="40" t="s">
         <v>267</v>
       </c>
       <c r="J7" s="2" t="s">
@@ -6658,19 +6808,19 @@
         <v>341</v>
       </c>
       <c r="V7" s="41" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="X7" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="Y7" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="Y7" s="41" t="s">
-        <v>357</v>
-      </c>
       <c r="Z7" s="41" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6683,7 +6833,7 @@
       <c r="D8" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="40" t="s">
         <v>244</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -6723,19 +6873,19 @@
       <c r="T8" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
       <c r="W8" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="X8" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="Y8" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="Z8" s="2" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6780,14 +6930,14 @@
       <c r="T9" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
       <c r="W9" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="X9" s="2"/>
       <c r="Y9" s="2" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="Z9" s="2"/>
     </row>
@@ -6825,14 +6975,14 @@
       <c r="T10" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
       <c r="W10" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="Z10" s="2"/>
     </row>
@@ -6864,10 +7014,10 @@
       <c r="T11" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="U11" s="49"/>
-      <c r="V11" s="49"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
       <c r="W11" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
@@ -6897,10 +7047,10 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
       <c r="W12" s="40" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
@@ -6927,8 +7077,8 @@
       <c r="R13" s="10"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="49"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
@@ -6954,8 +7104,8 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="49"/>
-      <c r="V14" s="49"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
@@ -6981,8 +7131,8 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="49"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
@@ -7008,8 +7158,8 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="49"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
@@ -7035,8 +7185,8 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
@@ -7062,8 +7212,8 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
@@ -7089,8 +7239,8 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
@@ -7106,12 +7256,18 @@
       <c r="B22" s="4" t="s">
         <v>234</v>
       </c>
+      <c r="Q22" s="4" t="s">
+        <v>358</v>
+      </c>
       <c r="V22" s="4"/>
     </row>
     <row r="23" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="36" t="s">
         <v>233</v>
       </c>
+      <c r="Q23" s="4" t="s">
+        <v>359</v>
+      </c>
       <c r="V23" s="4"/>
     </row>
     <row r="24" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -7124,85 +7280,75 @@
       <c r="B25" s="4" t="s">
         <v>236</v>
       </c>
+      <c r="Q25" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="R25" s="35"/>
       <c r="V25" s="4"/>
     </row>
     <row r="26" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4"/>
+      <c r="Q26" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="V26" s="4"/>
+    </row>
+    <row r="27" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C27" s="49" t="s">
         <v>230</v>
       </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="K26" s="3" t="s">
+      <c r="D27" s="50"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="K27" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="27" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="32" t="s">
+      <c r="Q27" s="17" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C28" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D28" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="33" t="s">
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="I27" s="44"/>
-      <c r="K27" s="32" t="s">
+      <c r="I28" s="44"/>
+      <c r="K28" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="L27" s="32" t="s">
+      <c r="L28" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-    </row>
-    <row r="28" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="31">
-        <v>0</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="I28" s="31"/>
-      <c r="K28" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L28" s="4">
-        <v>1</v>
-      </c>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="Q28" s="17" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="29" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" s="31">
         <v>0</v>
@@ -7210,10 +7356,12 @@
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
       <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
+      <c r="H29" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="I29" s="31"/>
       <c r="K29" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
@@ -7224,10 +7372,10 @@
     </row>
     <row r="30" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D30" s="31">
         <v>0</v>
@@ -7238,21 +7386,24 @@
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L30" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
+      <c r="Q30" s="4" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="31" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="D31" s="31">
         <v>0</v>
@@ -7262,13 +7413,25 @@
       <c r="G31" s="31"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
+      <c r="K31" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="L31" s="4">
+        <v>7</v>
+      </c>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="Q31" s="17" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="32" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D32" s="31">
         <v>0</v>
@@ -7278,35 +7441,37 @@
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-    </row>
-    <row r="33" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q32" s="17" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="D33" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
-      <c r="H33" s="31" t="s">
-        <v>227</v>
-      </c>
+      <c r="H33" s="31"/>
       <c r="I33" s="31"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-    </row>
-    <row r="34" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q33" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+    </row>
+    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" s="31">
         <v>1</v>
@@ -7314,17 +7479,20 @@
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
       <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
+      <c r="H34" s="31" t="s">
+        <v>227</v>
+      </c>
       <c r="I34" s="31"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-    </row>
-    <row r="35" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q34" s="47" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D35" s="31">
         <v>1</v>
@@ -7334,14 +7502,14 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
-      <c r="T35" s="6"/>
-    </row>
-    <row r="36" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q35" s="4"/>
+    </row>
+    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="D36" s="31">
         <v>1</v>
@@ -7351,14 +7519,16 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
-      <c r="T36" s="6"/>
-    </row>
-    <row r="37" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q36" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D37" s="31">
         <v>1</v>
@@ -7368,131 +7538,160 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="31"/>
-    </row>
-    <row r="38" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="Q37" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+    </row>
+    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="4">
+        <v>10</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="D38" s="31">
+        <v>1</v>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="Q38" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+    </row>
+    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="34" t="s">
+      <c r="B39" s="4"/>
+      <c r="C39" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D39" s="34">
         <v>1</v>
       </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="4"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-    </row>
-    <row r="40" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="4" t="s">
-        <v>265</v>
-      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="Q39" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="T39" s="6"/>
+    </row>
+    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C41" s="42"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="Q40" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="T40" s="6"/>
+    </row>
+    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C41" s="17"/>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
+      <c r="Q41" s="4"/>
+    </row>
+    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" s="42"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="32" t="s">
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+    </row>
+    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C44" s="37" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="43" t="s">
+    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="43" t="s">
         <v>269</v>
-      </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="43" t="s">
-        <v>270</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="43" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="43" t="s">
         <v>272</v>
-      </c>
-      <c r="C47" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="43" t="s">
-        <v>273</v>
       </c>
       <c r="C48" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="25"/>
+      <c r="B49" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C49" s="4">
+        <v>2</v>
+      </c>
     </row>
     <row r="50" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="26"/>
-      <c r="J50" s="27"/>
+      <c r="B50" s="25"/>
     </row>
     <row r="51" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
+      <c r="B51" s="26"/>
+      <c r="J51" s="27"/>
     </row>
     <row r="52" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L52" s="4"/>
@@ -7500,167 +7699,165 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
     </row>
-    <row r="53" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
-      <c r="O54" s="25"/>
-    </row>
+    <row r="53" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
     </row>
     <row r="56" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="26"/>
-      <c r="O56" s="26"/>
-      <c r="P56" s="28"/>
-    </row>
-    <row r="57" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B56" s="25"/>
+    </row>
+    <row r="57" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="28"/>
+    </row>
     <row r="58" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="4"/>
-    </row>
+    <row r="62" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4"/>
     </row>
-    <row r="64" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="4"/>
-    </row>
+    <row r="64" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-    </row>
-    <row r="67" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="25"/>
-      <c r="L68" s="25"/>
-      <c r="M68" s="25"/>
-      <c r="N68" s="25"/>
-      <c r="O68" s="25"/>
-    </row>
+    </row>
+    <row r="67" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="26"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
+      <c r="B69" s="25"/>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="25"/>
+      <c r="O69" s="25"/>
     </row>
     <row r="70" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
+      <c r="B70" s="26"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
     </row>
     <row r="71" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-    </row>
-    <row r="72" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="L71" s="29"/>
+      <c r="M71" s="29"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="29"/>
+      <c r="P71" s="29"/>
+    </row>
+    <row r="72" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+    </row>
     <row r="73" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="25"/>
-      <c r="J74" s="6"/>
-    </row>
+    <row r="74" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="75" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="26"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
-      <c r="J75" s="29"/>
-    </row>
-    <row r="76" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B75" s="25"/>
+      <c r="J75" s="6"/>
+    </row>
+    <row r="76" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="26"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="29"/>
+    </row>
     <row r="77" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="4"/>
-    </row>
+    <row r="79" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
     </row>
     <row r="81" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="17"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="82" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="17"/>
     </row>
-    <row r="83" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="3"/>
-    </row>
+    <row r="83" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="17"/>
+    </row>
+    <row r="84" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="85" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="11"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="29"/>
-    </row>
-    <row r="86" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-    </row>
-    <row r="88" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="11"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="29"/>
+    </row>
+    <row r="87" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+    </row>
     <row r="89" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="3"/>
-    </row>
+    <row r="90" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="11"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-    </row>
-    <row r="92" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="11"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
     <row r="93" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="3"/>
-    </row>
+    <row r="96" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B97" s="22"/>
-      <c r="C97" s="22"/>
-      <c r="D97" s="22"/>
-      <c r="E97" s="22"/>
-      <c r="F97" s="22"/>
-      <c r="G97" s="22"/>
-      <c r="H97" s="2"/>
-    </row>
-    <row r="98" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
+      <c r="B98" s="22"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="2"/>
     </row>
     <row r="99" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="19"/>
@@ -7671,12 +7868,12 @@
       <c r="G99" s="19"/>
     </row>
     <row r="100" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="19"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19"/>
+      <c r="G100" s="19"/>
     </row>
     <row r="101" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="20"/>
@@ -7695,14 +7892,21 @@
       <c r="G102" s="20"/>
     </row>
     <row r="103" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="21"/>
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-    </row>
-    <row r="104" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+    </row>
+    <row r="104" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="21"/>
+      <c r="C104" s="21"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="21"/>
+      <c r="F104" s="21"/>
+      <c r="G104" s="21"/>
+    </row>
     <row r="105" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="107" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7820,16 +8024,17 @@
     <row r="219" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="220" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="221" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B44" r:id="rId1" xr:uid="{A12A56EA-DD77-4B21-B871-280B426AB998}"/>
-    <hyperlink ref="B45" r:id="rId2" xr:uid="{DD7C436D-41E7-4B88-8FE4-C01371E67673}"/>
-    <hyperlink ref="B46" r:id="rId3" xr:uid="{623163C2-ADE6-4237-BE63-CD3468F56975}"/>
-    <hyperlink ref="B47" r:id="rId4" xr:uid="{2177B22D-D58C-44B4-9E03-04463B2F31A7}"/>
-    <hyperlink ref="B48" r:id="rId5" xr:uid="{03FBBD7B-915A-49B1-BE50-253850FA5EA1}"/>
+    <hyperlink ref="B45" r:id="rId1" xr:uid="{A12A56EA-DD77-4B21-B871-280B426AB998}"/>
+    <hyperlink ref="B46" r:id="rId2" xr:uid="{DD7C436D-41E7-4B88-8FE4-C01371E67673}"/>
+    <hyperlink ref="B47" r:id="rId3" xr:uid="{623163C2-ADE6-4237-BE63-CD3468F56975}"/>
+    <hyperlink ref="B48" r:id="rId4" xr:uid="{2177B22D-D58C-44B4-9E03-04463B2F31A7}"/>
+    <hyperlink ref="B49" r:id="rId5" xr:uid="{03FBBD7B-915A-49B1-BE50-253850FA5EA1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId6"/>

--- a/1. Database Design/Java24 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java24 QuyenPhan Database Design.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AEBE31-D563-40CB-BB8F-A3EB2C3383D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74990CE-CDE6-47B6-9D80-BE2F6CA7D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21240" tabRatio="433" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="433" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
     <sheet name="B2. Mô hình logic" sheetId="2" r:id="rId2"/>
     <sheet name="B3. Cơ sở dữ liệu vật lý" sheetId="3" r:id="rId3"/>
     <sheet name="B4. Database" sheetId="4" r:id="rId4"/>
+    <sheet name="B5. Test Data" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1377,8 +1378,318 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E7E28B04-4935-48FA-9EE4-0A8256C19678}</author>
+    <author>tc={2B40F884-F16D-44BF-A880-C134F5C62DAC}</author>
+    <author>Quyen Ngoc Phan</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{E7E28B04-4935-48FA-9EE4-0A8256C19678}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</t>
+      </text>
+    </comment>
+    <comment ref="F41" authorId="1" shapeId="0" xr:uid="{2B40F884-F16D-44BF-A880-C134F5C62DAC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng hàng còn lại ở thời điểm hiện tại</t>
+      </text>
+    </comment>
+    <comment ref="D64" authorId="2" shapeId="0" xr:uid="{BB4A1090-3661-40A4-A3E5-1A3317FAC575}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Số lượng nhập vào tại thời điểm nào đó</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D80" authorId="2" shapeId="0" xr:uid="{D25767D9-FA9E-4A69-B32D-BA5E99BAF609}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F115" authorId="2" shapeId="0" xr:uid="{BC409BAB-04D9-4584-BA8E-99429087B821}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lúc tính tổng tiền
+Nhớ kèm thuế</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C122" authorId="2" shapeId="0" xr:uid="{8DEA7BAF-CE9F-4AC6-8037-56FB16EB5203}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Tiền mặt
+Thẻ ghị nợ
+Thẻ tín dụng
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D189" authorId="2" shapeId="0" xr:uid="{9BDC8936-92C9-43A1-9379-AB9B7024CE45}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G189" authorId="2" shapeId="0" xr:uid="{6AE8310D-3BF7-4201-92B2-A2B94D757B52}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D203" authorId="2" shapeId="0" xr:uid="{9B933F05-4824-40FF-A0CC-44296B8D3399}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G203" authorId="2" shapeId="0" xr:uid="{A1ACCF64-494E-4A04-BC4E-BB52726C36B4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C224" authorId="2" shapeId="0" xr:uid="{650603E4-1922-4F3D-BF57-A44480C7E756}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D224" authorId="2" shapeId="0" xr:uid="{23A98BCD-8F58-45E6-803E-7B59DCF7EE56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E224" authorId="2" shapeId="0" xr:uid="{2B9AFA3A-E429-42C7-BCF0-DD3595633DCF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+DATE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G224" authorId="2" shapeId="0" xr:uid="{90AC3731-A473-470A-BB5D-0A799C6457A9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="550">
   <si>
     <t>MatHang</t>
   </si>
@@ -2854,12 +3165,524 @@
   <si>
     <t>C25_AMOUNT</t>
   </si>
+  <si>
+    <t>Áo 1</t>
+  </si>
+  <si>
+    <t>Áo 2</t>
+  </si>
+  <si>
+    <t>Áo 3</t>
+  </si>
+  <si>
+    <t>Quần 4</t>
+  </si>
+  <si>
+    <t>Quần 5</t>
+  </si>
+  <si>
+    <t>Giày 6</t>
+  </si>
+  <si>
+    <t>Giày 7</t>
+  </si>
+  <si>
+    <t>Giày 8</t>
+  </si>
+  <si>
+    <t>Giày 9</t>
+  </si>
+  <si>
+    <t>Giày 10</t>
+  </si>
+  <si>
+    <t>Giép 11</t>
+  </si>
+  <si>
+    <t>Áo 12</t>
+  </si>
+  <si>
+    <t>Giép 13</t>
+  </si>
+  <si>
+    <t>Mũ 14</t>
+  </si>
+  <si>
+    <t>Mũ 15</t>
+  </si>
+  <si>
+    <t>Thắt lưng 16</t>
+  </si>
+  <si>
+    <t>Thắt lưng 17</t>
+  </si>
+  <si>
+    <t>Mũ 18</t>
+  </si>
+  <si>
+    <t>Túi xách 1</t>
+  </si>
+  <si>
+    <t>Túi xách 2</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>BLUE</t>
+  </si>
+  <si>
+    <t>BLACK</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>WHILTE</t>
+  </si>
+  <si>
+    <t>ORIGIN</t>
+  </si>
+  <si>
+    <t>GRAY</t>
+  </si>
+  <si>
+    <t>Size 'S' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'M' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'L' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'XL' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'XXL' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'S' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'M' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'L' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'XL' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'XXL' cho Nam</t>
+  </si>
+  <si>
+    <t>Fake 100 rows</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
+---
+ITEM, SIZE có ID lẻ: AMOUNT = 125, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
+ITEM, SIZE có ID chẵn: AMOUNT = 280, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20</t>
+  </si>
+  <si>
+    <t>Thiết kế sai C12_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C03_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>sysdate - whReceiptId</t>
+  </si>
+  <si>
+    <t>Fake 50 rows</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N1</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N2</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N3</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N4</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N5</t>
+  </si>
+  <si>
+    <t>Giày</t>
+  </si>
+  <si>
+    <t>Dép</t>
+  </si>
+  <si>
+    <t>Mũ</t>
+  </si>
+  <si>
+    <t>Thắt lưng</t>
+  </si>
+  <si>
+    <t>Túi xách</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng WAREHOUSE_RECEIPT, ITEM
+---
+ITEM, WH có ID lẻ: AMOUNT = 777, BUY_PRICE =  random(50, 200)
+ITEM, SIZE có ID chẵn: AMOUNT = 820, BUY_PRICE =  random(100, 200)</t>
+  </si>
+  <si>
+    <t>BUY_PRICE từ phiếu nhập kho = giá cao nhất hoặc phiếu nhập mới nhất</t>
+  </si>
+  <si>
+    <t>Sử dụng ITEM ID từ bảng ITEM và fake default path
+format: file:///images/shopping/s_item_id.png</t>
+  </si>
+  <si>
+    <t>10.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 1</t>
+  </si>
+  <si>
+    <t>12.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 2</t>
+  </si>
+  <si>
+    <t>14.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 3</t>
+  </si>
+  <si>
+    <t>16.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 4</t>
+  </si>
+  <si>
+    <t>18.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 5</t>
+  </si>
+  <si>
+    <t>Địa chỉ 6</t>
+  </si>
+  <si>
+    <t>Địa chỉ 7</t>
+  </si>
+  <si>
+    <t>Địa chỉ 8</t>
+  </si>
+  <si>
+    <t>Địa chỉ 9</t>
+  </si>
+  <si>
+    <t>Địa chỉ 10</t>
+  </si>
+  <si>
+    <t>20.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>26.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>28.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>T15 10 Khách Hàng</t>
+  </si>
+  <si>
+    <t>T18 10 Địa Chỉ</t>
+  </si>
+  <si>
+    <t>T16 5 Nhân Viên</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>Sử dụng ID(s) từ T09_ORDER
+DeliveryFee = random(20,30,40,50,60)
+VoucherId = random(1, maxC19Id)
+TotalOfMoney = 0, cập nhật tính tiền xử lý sau</t>
+  </si>
+  <si>
+    <t>Thẻ tín dụng</t>
+  </si>
+  <si>
+    <t>Ví điện tử</t>
+  </si>
+  <si>
+    <t>Quan trọng, cần có dữ liệu chính xác để demo nhiều trường hợp</t>
+  </si>
+  <si>
+    <t>Chờ xác nhận</t>
+  </si>
+  <si>
+    <t>Đang đóng gói</t>
+  </si>
+  <si>
+    <t>Đóng gói hoàn thành</t>
+  </si>
+  <si>
+    <t>Đang vận chuyển</t>
+  </si>
+  <si>
+    <t>Giao hàng thành công</t>
+  </si>
+  <si>
+    <t>Giao hàng thất bại</t>
+  </si>
+  <si>
+    <t>Hủy đơn hàng</t>
+  </si>
+  <si>
+    <t>-- 1. Đơn hàng từ 1 - 5 --&gt; Giao thành công (trạng thái từ 1 - 5)</t>
+  </si>
+  <si>
+    <t>Nhân viên 1</t>
+  </si>
+  <si>
+    <t>SYSDATE - max(STATUS_ID) - ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>-- 2 Đơn hàng từ 6 - 8 --&gt; Đóng gói thành công (trạng thái từ 1 - 3)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 2</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>-- 3. Đơn hàng từ 9 - 10 --&gt; Đang giao hàng (trạng thái từ 1 - 4)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 3</t>
+  </si>
+  <si>
+    <t>-- 4. Đơn hàng từ 11 - 12 --&gt; Hủy đơn hàng (trạng thái 7)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 4</t>
+  </si>
+  <si>
+    <t>-- 4. Đơn hàng từ 13  --&gt; Giao hàng thất bại (trạng thái 1,2,3,4,6)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 5</t>
+  </si>
+  <si>
+    <t>Lê Tèo</t>
+  </si>
+  <si>
+    <t>c1@gmal.com</t>
+  </si>
+  <si>
+    <t>c1def</t>
+  </si>
+  <si>
+    <t>$2a$12$w0bs0MW/O3nTyMhuv0r1jOjq2gOaxLxkZgms7u/khHRmtCh3S/Hpu</t>
+  </si>
+  <si>
+    <t>Văn An</t>
+  </si>
+  <si>
+    <t>c2@gmal.com</t>
+  </si>
+  <si>
+    <t>c2auto</t>
+  </si>
+  <si>
+    <t>Nguyễn A</t>
+  </si>
+  <si>
+    <t>c3@gmal.com</t>
+  </si>
+  <si>
+    <t>c3def</t>
+  </si>
+  <si>
+    <t>Phan Tuấn</t>
+  </si>
+  <si>
+    <t>c4@gmal.com</t>
+  </si>
+  <si>
+    <t>c4auto</t>
+  </si>
+  <si>
+    <t>Hoàng Tiên</t>
+  </si>
+  <si>
+    <t>c5@gmal.com</t>
+  </si>
+  <si>
+    <t>c5def</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc</t>
+  </si>
+  <si>
+    <t>c6@gmal.com</t>
+  </si>
+  <si>
+    <t>c6auto</t>
+  </si>
+  <si>
+    <t>Đoạn Tú</t>
+  </si>
+  <si>
+    <t>c7@gmal.com</t>
+  </si>
+  <si>
+    <t>c7def</t>
+  </si>
+  <si>
+    <t>Hoàng B</t>
+  </si>
+  <si>
+    <t>c8@gmal.com</t>
+  </si>
+  <si>
+    <t>c8auto</t>
+  </si>
+  <si>
+    <t>Lê Huân</t>
+  </si>
+  <si>
+    <t>c9@gmal.com</t>
+  </si>
+  <si>
+    <t>c9def</t>
+  </si>
+  <si>
+    <t>Nam Ban</t>
+  </si>
+  <si>
+    <t>c10@gmal.com</t>
+  </si>
+  <si>
+    <t>c10auto</t>
+  </si>
+  <si>
+    <t>nv10@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 10</t>
+  </si>
+  <si>
+    <t>nv9@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 9</t>
+  </si>
+  <si>
+    <t>nv8@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 8</t>
+  </si>
+  <si>
+    <t>nv7@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 7</t>
+  </si>
+  <si>
+    <t>nv6@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 6</t>
+  </si>
+  <si>
+    <t>nv5@gmail.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 5</t>
+  </si>
+  <si>
+    <t>nv4@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 4</t>
+  </si>
+  <si>
+    <t>nv3@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 3</t>
+  </si>
+  <si>
+    <t>nv2@gmal.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 2</t>
+  </si>
+  <si>
+    <t>nv1@gmal.com</t>
+  </si>
+  <si>
+    <t>nv1def</t>
+  </si>
+  <si>
+    <t>nv2auto</t>
+  </si>
+  <si>
+    <t>nv3def</t>
+  </si>
+  <si>
+    <t>nv4auto</t>
+  </si>
+  <si>
+    <t>nv5def</t>
+  </si>
+  <si>
+    <t>nv6auto</t>
+  </si>
+  <si>
+    <t>nv7def</t>
+  </si>
+  <si>
+    <t>nv8auto</t>
+  </si>
+  <si>
+    <t>nv9def</t>
+  </si>
+  <si>
+    <t>nv10auto</t>
+  </si>
+  <si>
+    <t>Lấy thông tin từ bảng Khách Hàng
+Người nhận + Id, SĐT 123456789, Địa Chỉ + id</t>
+  </si>
+  <si>
+    <t>Phòng cơ sở vật chất</t>
+  </si>
+  <si>
+    <t>Phòng quảng cáo</t>
+  </si>
+  <si>
+    <t>Phòng nhân sự</t>
+  </si>
+  <si>
+    <t>Phòng quản lý</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3015,6 +3838,48 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -3078,7 +3943,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3121,12 +3986,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3272,10 +4196,71 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3571,6 +4556,17 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E3" dT="2024-03-19T12:47:34.71" personId="{AF552595-C243-4DB1-82EA-E8F193E73D49}" id="{E7E28B04-4935-48FA-9EE4-0A8256C19678}">
+    <text>Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</text>
+  </threadedComment>
+  <threadedComment ref="F41" dT="2024-04-02T13:53:18.17" personId="{AF552595-C243-4DB1-82EA-E8F193E73D49}" id="{2B40F884-F16D-44BF-A880-C134F5C62DAC}">
+    <text>Số lượng hàng còn lại ở thời điểm hiện tại</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:M50"/>
@@ -4301,8 +5297,8 @@
     <row r="46" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6547,6 +7543,9 @@
       <c r="J2" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="M2" s="55" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="3" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
@@ -7297,10 +8296,10 @@
       <c r="B27" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="56" t="s">
         <v>230</v>
       </c>
-      <c r="D27" s="50"/>
+      <c r="D27" s="57"/>
       <c r="E27" s="35"/>
       <c r="F27" s="35"/>
       <c r="G27" s="35"/>
@@ -8039,4 +9038,3293 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId6"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C125E9-733D-4F85-B782-7EFA49F565B4}">
+  <dimension ref="B1:K1000"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="33" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="9" max="28" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+    </row>
+    <row r="3" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="53">
+        <v>1</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" s="53">
+        <v>1</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="53">
+        <v>2</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>384</v>
+      </c>
+      <c r="D5" s="53">
+        <v>1</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="53">
+        <v>3</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>385</v>
+      </c>
+      <c r="D6" s="53">
+        <v>1</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="53">
+        <v>4</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="53">
+        <v>2</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="53">
+        <v>5</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>387</v>
+      </c>
+      <c r="D8" s="53">
+        <v>2</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="53">
+        <v>6</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>388</v>
+      </c>
+      <c r="D9" s="53">
+        <v>3</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="53">
+        <v>7</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>389</v>
+      </c>
+      <c r="D10" s="53">
+        <v>3</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="53">
+        <v>8</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="53">
+        <v>3</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="53">
+        <v>9</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>391</v>
+      </c>
+      <c r="D12" s="53">
+        <v>3</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="53">
+        <v>10</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="53">
+        <v>3</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="53">
+        <v>11</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="D14" s="53">
+        <v>4</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="53">
+        <v>12</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>394</v>
+      </c>
+      <c r="D15" s="53">
+        <v>1</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="53">
+        <v>13</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>395</v>
+      </c>
+      <c r="D16" s="53">
+        <v>4</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="53">
+        <v>14</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="D17" s="53">
+        <v>5</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="53">
+        <v>15</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="53">
+        <v>5</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="53">
+        <v>16</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="53">
+        <v>6</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="53">
+        <v>17</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="D20" s="53">
+        <v>6</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="53">
+        <v>18</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>400</v>
+      </c>
+      <c r="D21" s="53">
+        <v>5</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="53">
+        <v>19</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>401</v>
+      </c>
+      <c r="D22" s="53">
+        <v>7</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="53">
+        <v>20</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="D23" s="53">
+        <v>7</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+    </row>
+    <row r="27" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="53">
+        <v>1</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="53">
+        <v>0</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="53">
+        <v>2</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="53">
+        <v>0</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="53">
+        <v>3</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="53">
+        <v>0</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="53">
+        <v>4</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" s="53">
+        <v>0</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="53">
+        <v>5</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="D32" s="53">
+        <v>0</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="53">
+        <v>6</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="53">
+        <v>1</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="53">
+        <v>7</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="53">
+        <v>1</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="53">
+        <v>8</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="53">
+        <v>1</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="53">
+        <v>9</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" s="53">
+        <v>1</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="53">
+        <v>10</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="53">
+        <v>1</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+    </row>
+    <row r="41" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="51" t="s">
+        <v>424</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="50" t="s">
+        <v>421</v>
+      </c>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+    </row>
+    <row r="43" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="50"/>
+      <c r="C43" s="58" t="s">
+        <v>422</v>
+      </c>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="50"/>
+    </row>
+    <row r="44" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="50"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="50"/>
+    </row>
+    <row r="45" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="50"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="50"/>
+    </row>
+    <row r="46" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="50"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="50"/>
+    </row>
+    <row r="47" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="44" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="63"/>
+    </row>
+    <row r="49" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="48" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="2">
+        <v>1</v>
+      </c>
+      <c r="C51" s="60" t="s">
+        <v>425</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="2">
+        <v>2</v>
+      </c>
+      <c r="C52" s="60"/>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="2">
+        <v>3</v>
+      </c>
+      <c r="C53" s="60"/>
+      <c r="D53" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="2">
+        <v>4</v>
+      </c>
+      <c r="C54" s="60"/>
+      <c r="D54" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="2">
+        <v>5</v>
+      </c>
+      <c r="C55" s="60"/>
+      <c r="D55" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="2">
+        <v>6</v>
+      </c>
+      <c r="C56" s="60"/>
+      <c r="D56" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="2">
+        <v>7</v>
+      </c>
+      <c r="C57" s="60"/>
+      <c r="D57" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="2">
+        <v>8</v>
+      </c>
+      <c r="C58" s="60"/>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="2">
+        <v>9</v>
+      </c>
+      <c r="C59" s="60"/>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="2">
+        <v>10</v>
+      </c>
+      <c r="C60" s="60"/>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="48" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="C64" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F64" s="40" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="C65" s="61" t="s">
+        <v>437</v>
+      </c>
+      <c r="D65" s="62"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="62"/>
+    </row>
+    <row r="66" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+    </row>
+    <row r="67" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="59"/>
+    </row>
+    <row r="68" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="59"/>
+      <c r="D68" s="59"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="59"/>
+    </row>
+    <row r="69" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="48" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="2">
+        <v>1</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D72" s="2">
+        <v>147258369</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="2">
+        <v>2</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D73" s="2">
+        <v>247258369</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="2">
+        <v>3</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D74" s="2">
+        <v>347258369</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="2">
+        <v>4</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D75" s="2">
+        <v>447258369</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="2">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D76" s="2">
+        <v>547258369</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="C79" s="50"/>
+    </row>
+    <row r="80" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="2">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="2">
+        <v>2</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D82" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="2">
+        <v>3</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D83" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="2">
+        <v>4</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="2">
+        <v>5</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="2">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D86" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="2">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D87" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="48" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C91" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="61" t="s">
+        <v>439</v>
+      </c>
+      <c r="C92" s="62"/>
+    </row>
+    <row r="93" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="59"/>
+      <c r="C93" s="59"/>
+    </row>
+    <row r="94" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="59"/>
+      <c r="C94" s="59"/>
+    </row>
+    <row r="95" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="48" t="s">
+        <v>275</v>
+      </c>
+      <c r="E97" s="50" t="s">
+        <v>458</v>
+      </c>
+      <c r="F97" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="G97" s="50" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D98" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="E98" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="F98" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="G98" s="40" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="53">
+        <v>1</v>
+      </c>
+      <c r="C99" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D99" s="53">
+        <v>1</v>
+      </c>
+      <c r="E99" s="53">
+        <v>1</v>
+      </c>
+      <c r="F99" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="53">
+        <v>2</v>
+      </c>
+      <c r="C100" s="64" t="s">
+        <v>442</v>
+      </c>
+      <c r="D100" s="53">
+        <v>2</v>
+      </c>
+      <c r="E100" s="53">
+        <v>2</v>
+      </c>
+      <c r="F100" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="53">
+        <v>3</v>
+      </c>
+      <c r="C101" s="64" t="s">
+        <v>444</v>
+      </c>
+      <c r="D101" s="53">
+        <v>3</v>
+      </c>
+      <c r="E101" s="53">
+        <v>3</v>
+      </c>
+      <c r="F101" s="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="53">
+        <v>4</v>
+      </c>
+      <c r="C102" s="64" t="s">
+        <v>446</v>
+      </c>
+      <c r="D102" s="53">
+        <v>4</v>
+      </c>
+      <c r="E102" s="53">
+        <v>4</v>
+      </c>
+      <c r="F102" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="53">
+        <v>5</v>
+      </c>
+      <c r="C103" s="64" t="s">
+        <v>448</v>
+      </c>
+      <c r="D103" s="53">
+        <v>5</v>
+      </c>
+      <c r="E103" s="53">
+        <v>5</v>
+      </c>
+      <c r="F103" s="53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="53">
+        <v>6</v>
+      </c>
+      <c r="C104" s="64" t="s">
+        <v>442</v>
+      </c>
+      <c r="D104" s="53">
+        <v>6</v>
+      </c>
+      <c r="E104" s="53">
+        <v>6</v>
+      </c>
+      <c r="F104" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="53">
+        <v>7</v>
+      </c>
+      <c r="C105" s="64" t="s">
+        <v>444</v>
+      </c>
+      <c r="D105" s="53">
+        <v>7</v>
+      </c>
+      <c r="E105" s="53">
+        <v>7</v>
+      </c>
+      <c r="F105" s="53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="53">
+        <v>8</v>
+      </c>
+      <c r="C106" s="64" t="s">
+        <v>448</v>
+      </c>
+      <c r="D106" s="53">
+        <v>8</v>
+      </c>
+      <c r="E106" s="53">
+        <v>8</v>
+      </c>
+      <c r="F106" s="53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="53">
+        <v>9</v>
+      </c>
+      <c r="C107" s="64" t="s">
+        <v>448</v>
+      </c>
+      <c r="D107" s="53">
+        <v>9</v>
+      </c>
+      <c r="E107" s="53">
+        <v>9</v>
+      </c>
+      <c r="F107" s="53">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="53">
+        <v>10</v>
+      </c>
+      <c r="C108" s="64" t="s">
+        <v>448</v>
+      </c>
+      <c r="D108" s="53">
+        <v>10</v>
+      </c>
+      <c r="E108" s="53">
+        <v>10</v>
+      </c>
+      <c r="F108" s="53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="53">
+        <v>11</v>
+      </c>
+      <c r="C109" s="64" t="s">
+        <v>455</v>
+      </c>
+      <c r="D109" s="53">
+        <v>11</v>
+      </c>
+      <c r="E109" s="53">
+        <v>2</v>
+      </c>
+      <c r="F109" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="53">
+        <v>12</v>
+      </c>
+      <c r="C110" s="64" t="s">
+        <v>456</v>
+      </c>
+      <c r="D110" s="53">
+        <v>12</v>
+      </c>
+      <c r="E110" s="53">
+        <v>4</v>
+      </c>
+      <c r="F110" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="53">
+        <v>13</v>
+      </c>
+      <c r="C111" s="64" t="s">
+        <v>457</v>
+      </c>
+      <c r="D111" s="53">
+        <v>13</v>
+      </c>
+      <c r="E111" s="53">
+        <v>6</v>
+      </c>
+      <c r="F111" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="48" t="s">
+        <v>300</v>
+      </c>
+      <c r="E114" s="50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C115" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="61" t="s">
+        <v>462</v>
+      </c>
+      <c r="C116" s="62"/>
+      <c r="D116" s="62"/>
+      <c r="E116" s="62"/>
+      <c r="F116" s="62"/>
+    </row>
+    <row r="117" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="59"/>
+      <c r="C117" s="59"/>
+      <c r="D117" s="59"/>
+      <c r="E117" s="59"/>
+      <c r="F117" s="59"/>
+    </row>
+    <row r="118" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="59"/>
+      <c r="C118" s="59"/>
+      <c r="D118" s="59"/>
+      <c r="E118" s="59"/>
+      <c r="F118" s="59"/>
+    </row>
+    <row r="119" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="48" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="53">
+        <v>1</v>
+      </c>
+      <c r="C123" s="53" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="53">
+        <v>2</v>
+      </c>
+      <c r="C124" s="53" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="53">
+        <v>3</v>
+      </c>
+      <c r="C125" s="53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="53">
+        <v>4</v>
+      </c>
+      <c r="C126" s="53" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="48" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="41" t="s">
+        <v>283</v>
+      </c>
+      <c r="C130" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="65" t="s">
+        <v>465</v>
+      </c>
+      <c r="C131" s="66"/>
+      <c r="D131" s="67"/>
+    </row>
+    <row r="132" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="53">
+        <v>1</v>
+      </c>
+      <c r="C132" s="53">
+        <v>1</v>
+      </c>
+      <c r="D132" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="53">
+        <v>1</v>
+      </c>
+      <c r="C133" s="53">
+        <v>3</v>
+      </c>
+      <c r="D133" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="53">
+        <v>2</v>
+      </c>
+      <c r="C134" s="53">
+        <v>4</v>
+      </c>
+      <c r="D134" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="53">
+        <v>2</v>
+      </c>
+      <c r="C135" s="53">
+        <v>5</v>
+      </c>
+      <c r="D135" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="53">
+        <v>3</v>
+      </c>
+      <c r="C136" s="53">
+        <v>6</v>
+      </c>
+      <c r="D136" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="53">
+        <v>3</v>
+      </c>
+      <c r="C137" s="53">
+        <v>2</v>
+      </c>
+      <c r="D137" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="53">
+        <v>4</v>
+      </c>
+      <c r="C138" s="53">
+        <v>8</v>
+      </c>
+      <c r="D138" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="53">
+        <v>4</v>
+      </c>
+      <c r="C139" s="53">
+        <v>12</v>
+      </c>
+      <c r="D139" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="53">
+        <v>5</v>
+      </c>
+      <c r="C140" s="53">
+        <v>88</v>
+      </c>
+      <c r="D140" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="53">
+        <v>5</v>
+      </c>
+      <c r="C141" s="53">
+        <v>22</v>
+      </c>
+      <c r="D141" s="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="53">
+        <v>5</v>
+      </c>
+      <c r="C142" s="53">
+        <v>11</v>
+      </c>
+      <c r="D142" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="53">
+        <v>5</v>
+      </c>
+      <c r="C143" s="53">
+        <v>33</v>
+      </c>
+      <c r="D143" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="53">
+        <v>6</v>
+      </c>
+      <c r="C144" s="53">
+        <v>2</v>
+      </c>
+      <c r="D144" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="53">
+        <v>7</v>
+      </c>
+      <c r="C145" s="53">
+        <v>1</v>
+      </c>
+      <c r="D145" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="53">
+        <v>8</v>
+      </c>
+      <c r="C146" s="53">
+        <v>27</v>
+      </c>
+      <c r="D146" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="53">
+        <v>8</v>
+      </c>
+      <c r="C147" s="53">
+        <v>23</v>
+      </c>
+      <c r="D147" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="53">
+        <v>8</v>
+      </c>
+      <c r="C148" s="53">
+        <v>98</v>
+      </c>
+      <c r="D148" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="53">
+        <v>9</v>
+      </c>
+      <c r="C149" s="53">
+        <v>100</v>
+      </c>
+      <c r="D149" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="53">
+        <v>9</v>
+      </c>
+      <c r="C150" s="53">
+        <v>11</v>
+      </c>
+      <c r="D150" s="53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="53">
+        <v>9</v>
+      </c>
+      <c r="C151" s="53">
+        <v>45</v>
+      </c>
+      <c r="D151" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="53">
+        <v>9</v>
+      </c>
+      <c r="C152" s="53">
+        <v>22</v>
+      </c>
+      <c r="D152" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="53">
+        <v>9</v>
+      </c>
+      <c r="C153" s="53">
+        <v>32</v>
+      </c>
+      <c r="D153" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="53">
+        <v>10</v>
+      </c>
+      <c r="C154" s="53">
+        <v>18</v>
+      </c>
+      <c r="D154" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="53">
+        <v>10</v>
+      </c>
+      <c r="C155" s="53">
+        <v>29</v>
+      </c>
+      <c r="D155" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="53">
+        <v>11</v>
+      </c>
+      <c r="C156" s="53">
+        <v>33</v>
+      </c>
+      <c r="D156" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="53">
+        <v>11</v>
+      </c>
+      <c r="C157" s="53">
+        <v>65</v>
+      </c>
+      <c r="D157" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="53">
+        <v>11</v>
+      </c>
+      <c r="C158" s="53">
+        <v>1</v>
+      </c>
+      <c r="D158" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="53">
+        <v>11</v>
+      </c>
+      <c r="C159" s="53">
+        <v>2</v>
+      </c>
+      <c r="D159" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="53">
+        <v>11</v>
+      </c>
+      <c r="C160" s="53">
+        <v>5</v>
+      </c>
+      <c r="D160" s="53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="53">
+        <v>11</v>
+      </c>
+      <c r="C161" s="53">
+        <v>7</v>
+      </c>
+      <c r="D161" s="53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="53">
+        <v>12</v>
+      </c>
+      <c r="C162" s="53">
+        <v>55</v>
+      </c>
+      <c r="D162" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="53">
+        <v>13</v>
+      </c>
+      <c r="C163" s="53">
+        <v>92</v>
+      </c>
+      <c r="D163" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="53">
+        <v>13</v>
+      </c>
+      <c r="C164" s="53">
+        <v>14</v>
+      </c>
+      <c r="D164" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="48" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="53">
+        <v>1</v>
+      </c>
+      <c r="C169" s="53" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="53">
+        <v>2</v>
+      </c>
+      <c r="C170" s="53" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="53">
+        <v>3</v>
+      </c>
+      <c r="C171" s="53" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="53">
+        <v>4</v>
+      </c>
+      <c r="C172" s="53" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B173" s="53">
+        <v>5</v>
+      </c>
+      <c r="C173" s="53" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="53">
+        <v>6</v>
+      </c>
+      <c r="C174" s="53" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="53">
+        <v>7</v>
+      </c>
+      <c r="C175" s="53" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="48" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="C179" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="D179" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B180" s="68" t="s">
+        <v>473</v>
+      </c>
+      <c r="C180" s="50"/>
+      <c r="D180" s="50" t="s">
+        <v>474</v>
+      </c>
+      <c r="E180" s="50" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="181" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B181" s="68" t="s">
+        <v>476</v>
+      </c>
+      <c r="C181" s="50"/>
+      <c r="D181" s="50" t="s">
+        <v>477</v>
+      </c>
+      <c r="E181" s="69" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="182" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="68" t="s">
+        <v>479</v>
+      </c>
+      <c r="C182" s="50"/>
+      <c r="D182" s="50" t="s">
+        <v>480</v>
+      </c>
+      <c r="E182" s="69" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="183" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="68" t="s">
+        <v>481</v>
+      </c>
+      <c r="C183" s="50"/>
+      <c r="D183" s="50" t="s">
+        <v>482</v>
+      </c>
+      <c r="E183" s="69" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="184" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B184" s="68" t="s">
+        <v>483</v>
+      </c>
+      <c r="C184" s="50"/>
+      <c r="D184" s="50" t="s">
+        <v>484</v>
+      </c>
+      <c r="E184" s="50"/>
+    </row>
+    <row r="185" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B188" s="48" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="189" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B189" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J189" s="48" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="190" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B190" s="53">
+        <v>1</v>
+      </c>
+      <c r="C190" s="53" t="s">
+        <v>485</v>
+      </c>
+      <c r="D190" s="64" t="s">
+        <v>486</v>
+      </c>
+      <c r="E190" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="F190" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G190" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H190" s="53" t="s">
+        <v>487</v>
+      </c>
+      <c r="J190" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="K190" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="191" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B191" s="53">
+        <v>2</v>
+      </c>
+      <c r="C191" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="D191" s="53" t="s">
+        <v>490</v>
+      </c>
+      <c r="E191" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="F191" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G191" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H191" s="53" t="s">
+        <v>491</v>
+      </c>
+      <c r="J191" s="53">
+        <v>1</v>
+      </c>
+      <c r="K191" s="53" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="192" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B192" s="53">
+        <v>3</v>
+      </c>
+      <c r="C192" s="53" t="s">
+        <v>492</v>
+      </c>
+      <c r="D192" s="53" t="s">
+        <v>493</v>
+      </c>
+      <c r="E192" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="F192" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G192" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H192" s="53" t="s">
+        <v>494</v>
+      </c>
+      <c r="J192" s="53">
+        <v>2</v>
+      </c>
+      <c r="K192" s="53" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="193" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="53">
+        <v>4</v>
+      </c>
+      <c r="C193" s="53" t="s">
+        <v>495</v>
+      </c>
+      <c r="D193" s="53" t="s">
+        <v>496</v>
+      </c>
+      <c r="E193" s="53" t="s">
+        <v>447</v>
+      </c>
+      <c r="F193" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G193" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H193" s="53" t="s">
+        <v>497</v>
+      </c>
+      <c r="J193" s="53">
+        <v>3</v>
+      </c>
+      <c r="K193" s="53" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="194" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B194" s="53">
+        <v>5</v>
+      </c>
+      <c r="C194" s="53" t="s">
+        <v>498</v>
+      </c>
+      <c r="D194" s="53" t="s">
+        <v>499</v>
+      </c>
+      <c r="E194" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="F194" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G194" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H194" s="53" t="s">
+        <v>500</v>
+      </c>
+      <c r="J194" s="53">
+        <v>4</v>
+      </c>
+      <c r="K194" s="53" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="195" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B195" s="53">
+        <v>6</v>
+      </c>
+      <c r="C195" s="53" t="s">
+        <v>501</v>
+      </c>
+      <c r="D195" s="53" t="s">
+        <v>502</v>
+      </c>
+      <c r="E195" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="F195" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G195" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H195" s="53" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B196" s="53">
+        <v>7</v>
+      </c>
+      <c r="C196" s="53" t="s">
+        <v>504</v>
+      </c>
+      <c r="D196" s="53" t="s">
+        <v>505</v>
+      </c>
+      <c r="E196" s="53" t="s">
+        <v>451</v>
+      </c>
+      <c r="F196" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G196" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H196" s="53" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B197" s="53">
+        <v>8</v>
+      </c>
+      <c r="C197" s="53" t="s">
+        <v>507</v>
+      </c>
+      <c r="D197" s="53" t="s">
+        <v>508</v>
+      </c>
+      <c r="E197" s="53" t="s">
+        <v>452</v>
+      </c>
+      <c r="F197" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G197" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H197" s="53" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="198" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B198" s="53">
+        <v>9</v>
+      </c>
+      <c r="C198" s="53" t="s">
+        <v>510</v>
+      </c>
+      <c r="D198" s="53" t="s">
+        <v>511</v>
+      </c>
+      <c r="E198" s="53" t="s">
+        <v>453</v>
+      </c>
+      <c r="F198" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G198" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H198" s="53" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="53">
+        <v>10</v>
+      </c>
+      <c r="C199" s="53" t="s">
+        <v>513</v>
+      </c>
+      <c r="D199" s="53" t="s">
+        <v>514</v>
+      </c>
+      <c r="E199" s="53" t="s">
+        <v>454</v>
+      </c>
+      <c r="F199" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G199" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H199" s="53" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="200" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="48" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B203" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I203" s="40" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="204" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B204" s="53">
+        <v>1</v>
+      </c>
+      <c r="C204" s="53" t="s">
+        <v>474</v>
+      </c>
+      <c r="D204" s="64" t="s">
+        <v>534</v>
+      </c>
+      <c r="E204" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="F204" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G204" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H204" s="53" t="s">
+        <v>535</v>
+      </c>
+      <c r="I204" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B205" s="53">
+        <v>2</v>
+      </c>
+      <c r="C205" s="53" t="s">
+        <v>533</v>
+      </c>
+      <c r="D205" s="53" t="s">
+        <v>532</v>
+      </c>
+      <c r="E205" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="F205" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G205" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H205" s="53" t="s">
+        <v>536</v>
+      </c>
+      <c r="I205" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="53">
+        <v>3</v>
+      </c>
+      <c r="C206" s="53" t="s">
+        <v>531</v>
+      </c>
+      <c r="D206" s="64" t="s">
+        <v>530</v>
+      </c>
+      <c r="E206" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="F206" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G206" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H206" s="53" t="s">
+        <v>537</v>
+      </c>
+      <c r="I206" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B207" s="53">
+        <v>4</v>
+      </c>
+      <c r="C207" s="53" t="s">
+        <v>529</v>
+      </c>
+      <c r="D207" s="53" t="s">
+        <v>528</v>
+      </c>
+      <c r="E207" s="53" t="s">
+        <v>447</v>
+      </c>
+      <c r="F207" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G207" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H207" s="53" t="s">
+        <v>538</v>
+      </c>
+      <c r="I207" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B208" s="53">
+        <v>5</v>
+      </c>
+      <c r="C208" s="53" t="s">
+        <v>527</v>
+      </c>
+      <c r="D208" s="64" t="s">
+        <v>526</v>
+      </c>
+      <c r="E208" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="F208" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G208" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H208" s="53" t="s">
+        <v>539</v>
+      </c>
+      <c r="I208" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B209" s="53">
+        <v>6</v>
+      </c>
+      <c r="C209" s="53" t="s">
+        <v>525</v>
+      </c>
+      <c r="D209" s="53" t="s">
+        <v>524</v>
+      </c>
+      <c r="E209" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="F209" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G209" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H209" s="53" t="s">
+        <v>540</v>
+      </c>
+      <c r="I209" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B210" s="53">
+        <v>7</v>
+      </c>
+      <c r="C210" s="53" t="s">
+        <v>523</v>
+      </c>
+      <c r="D210" s="64" t="s">
+        <v>522</v>
+      </c>
+      <c r="E210" s="53" t="s">
+        <v>451</v>
+      </c>
+      <c r="F210" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G210" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H210" s="53" t="s">
+        <v>541</v>
+      </c>
+      <c r="I210" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B211" s="53">
+        <v>8</v>
+      </c>
+      <c r="C211" s="53" t="s">
+        <v>521</v>
+      </c>
+      <c r="D211" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="E211" s="53" t="s">
+        <v>452</v>
+      </c>
+      <c r="F211" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G211" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H211" s="53" t="s">
+        <v>542</v>
+      </c>
+      <c r="I211" s="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B212" s="53">
+        <v>9</v>
+      </c>
+      <c r="C212" s="53" t="s">
+        <v>519</v>
+      </c>
+      <c r="D212" s="64" t="s">
+        <v>518</v>
+      </c>
+      <c r="E212" s="53" t="s">
+        <v>453</v>
+      </c>
+      <c r="F212" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G212" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H212" s="53" t="s">
+        <v>543</v>
+      </c>
+      <c r="I212" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B213" s="53">
+        <v>10</v>
+      </c>
+      <c r="C213" s="53" t="s">
+        <v>517</v>
+      </c>
+      <c r="D213" s="53" t="s">
+        <v>516</v>
+      </c>
+      <c r="E213" s="53" t="s">
+        <v>454</v>
+      </c>
+      <c r="F213" s="53">
+        <v>123456789</v>
+      </c>
+      <c r="G213" s="70" t="s">
+        <v>488</v>
+      </c>
+      <c r="H213" s="53" t="s">
+        <v>544</v>
+      </c>
+      <c r="I213" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B216" s="48" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="217" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C217" s="40" t="s">
+        <v>328</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="218" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="61" t="s">
+        <v>545</v>
+      </c>
+      <c r="C218" s="62"/>
+      <c r="D218" s="62"/>
+      <c r="E218" s="62"/>
+      <c r="F218" s="62"/>
+    </row>
+    <row r="219" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="59"/>
+      <c r="C219" s="59"/>
+      <c r="D219" s="59"/>
+      <c r="E219" s="59"/>
+      <c r="F219" s="59"/>
+    </row>
+    <row r="220" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="59"/>
+      <c r="C220" s="59"/>
+      <c r="D220" s="59"/>
+      <c r="E220" s="59"/>
+      <c r="F220" s="59"/>
+    </row>
+    <row r="221" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="48" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="224" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B224" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" s="71" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B233" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C233" s="38" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B241" s="48" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B242" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="C242" s="41" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="B218:F220"/>
+    <mergeCell ref="C43:F46"/>
+    <mergeCell ref="C51:C60"/>
+    <mergeCell ref="C65:F68"/>
+    <mergeCell ref="B92:C94"/>
+    <mergeCell ref="B116:F118"/>
+  </mergeCells>
+  <phoneticPr fontId="25" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/1. Database Design/Java24 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java24 QuyenPhan Database Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74990CE-CDE6-47B6-9D80-BE2F6CA7D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23D08ED-37A7-4DD8-B3BC-B88D23C37480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="433" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1689,7 +1689,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="553">
   <si>
     <t>MatHang</t>
   </si>
@@ -3298,9 +3298,6 @@
     <t>sysdate - whReceiptId</t>
   </si>
   <si>
-    <t>Fake 50 rows</t>
-  </si>
-  <si>
     <t>Nhà cung cấp N1</t>
   </si>
   <si>
@@ -3329,15 +3326,6 @@
   </si>
   <si>
     <t>Túi xách</t>
-  </si>
-  <si>
-    <t>Sử dụng dữ liệu từ các bảng WAREHOUSE_RECEIPT, ITEM
----
-ITEM, WH có ID lẻ: AMOUNT = 777, BUY_PRICE =  random(50, 200)
-ITEM, SIZE có ID chẵn: AMOUNT = 820, BUY_PRICE =  random(100, 200)</t>
-  </si>
-  <si>
-    <t>BUY_PRICE từ phiếu nhập kho = giá cao nhất hoặc phiếu nhập mới nhất</t>
   </si>
   <si>
     <t>Sử dụng ITEM ID từ bảng ITEM và fake default path
@@ -3575,61 +3563,31 @@
     <t>c10auto</t>
   </si>
   <si>
-    <t>nv10@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 10</t>
   </si>
   <si>
-    <t>nv9@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 9</t>
   </si>
   <si>
-    <t>nv8@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 8</t>
   </si>
   <si>
-    <t>nv7@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 7</t>
   </si>
   <si>
-    <t>nv6@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 6</t>
   </si>
   <si>
-    <t>nv5@gmail.com</t>
-  </si>
-  <si>
     <t>Nhân viên 5</t>
   </si>
   <si>
-    <t>nv4@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 4</t>
   </si>
   <si>
-    <t>nv3@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 3</t>
   </si>
   <si>
-    <t>nv2@gmal.com</t>
-  </si>
-  <si>
     <t>Nhân viên 2</t>
-  </si>
-  <si>
-    <t>nv1@gmal.com</t>
   </si>
   <si>
     <t>nv1def</t>
@@ -3676,13 +3634,77 @@
   </si>
   <si>
     <t>Phòng quản lý</t>
+  </si>
+  <si>
+    <t>T07</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>formula procedure</t>
+  </si>
+  <si>
+    <t>T01</t>
+  </si>
+  <si>
+    <t>T02</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BUY_PRICE từ phiếu nhập kho = giá cao nhất hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>phiếu nhập mới nhất</t>
+    </r>
+  </si>
+  <si>
+    <t>T05</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng WAREHOUSE_RECEIPT, ITEM
+---
+ITEM, WH có ID lẻ: AMOUNT = 777, BUY_PRICE =  random(50, 200)
+ITEM, WH có ID chẵn: AMOUNT = 820, BUY_PRICE =  random(100, 200)</t>
+  </si>
+  <si>
+    <t>T06</t>
+  </si>
+  <si>
+    <t>T01 T04</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>hardcode</t>
+  </si>
+  <si>
+    <t>nv1@gmail.com</t>
+  </si>
+  <si>
+    <t>nv2@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3880,8 +3902,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3939,6 +3969,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4050,7 +4086,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4217,38 +4253,8 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -4261,6 +4267,48 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8296,10 +8344,10 @@
       <c r="B27" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="62" t="s">
         <v>230</v>
       </c>
-      <c r="D27" s="57"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="35"/>
       <c r="F27" s="35"/>
       <c r="G27" s="35"/>
@@ -9042,10 +9090,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C125E9-733D-4F85-B782-7EFA49F565B4}">
-  <dimension ref="B1:K1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="50" customWidth="1"/>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
@@ -9056,16 +9104,21 @@
     <col min="9" max="28" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
+        <v>538</v>
+      </c>
+      <c r="B2" s="74" t="s">
         <v>215</v>
       </c>
       <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="D2" s="50" t="s">
+        <v>537</v>
+      </c>
       <c r="E2" s="50"/>
     </row>
-    <row r="3" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="51" t="s">
         <v>216</v>
       </c>
@@ -9079,7 +9132,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="53">
         <v>1</v>
       </c>
@@ -9093,7 +9146,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53">
         <v>2</v>
       </c>
@@ -9107,7 +9160,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="53">
         <v>3</v>
       </c>
@@ -9121,7 +9174,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="53">
         <v>4</v>
       </c>
@@ -9135,7 +9188,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="53">
         <v>5</v>
       </c>
@@ -9149,7 +9202,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="53">
         <v>6</v>
       </c>
@@ -9163,7 +9216,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="53">
         <v>7</v>
       </c>
@@ -9177,7 +9230,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="53">
         <v>8</v>
       </c>
@@ -9191,7 +9244,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="53">
         <v>9</v>
       </c>
@@ -9205,7 +9258,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="53">
         <v>10</v>
       </c>
@@ -9219,7 +9272,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="53">
         <v>11</v>
       </c>
@@ -9233,7 +9286,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="53">
         <v>12</v>
       </c>
@@ -9247,7 +9300,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="53">
         <v>13</v>
       </c>
@@ -9261,7 +9314,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="53">
         <v>14</v>
       </c>
@@ -9275,7 +9328,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="53">
         <v>15</v>
       </c>
@@ -9289,7 +9342,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="53">
         <v>16</v>
       </c>
@@ -9303,7 +9356,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="53">
         <v>17</v>
       </c>
@@ -9317,7 +9370,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="53">
         <v>18</v>
       </c>
@@ -9331,7 +9384,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="53">
         <v>19</v>
       </c>
@@ -9345,7 +9398,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="53">
         <v>20</v>
       </c>
@@ -9359,17 +9412,20 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="49" t="s">
+    <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="50" t="s">
+        <v>540</v>
+      </c>
+      <c r="B26" s="74" t="s">
         <v>218</v>
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="50"/>
       <c r="E26" s="50"/>
     </row>
-    <row r="27" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="51" t="s">
         <v>219</v>
       </c>
@@ -9383,7 +9439,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="53">
         <v>1</v>
       </c>
@@ -9397,7 +9453,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="53">
         <v>2</v>
       </c>
@@ -9411,7 +9467,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="53">
         <v>3</v>
       </c>
@@ -9425,7 +9481,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="31" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="53">
         <v>4</v>
       </c>
@@ -9439,7 +9495,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="32" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="53">
         <v>5</v>
       </c>
@@ -9453,7 +9509,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="53">
         <v>6</v>
       </c>
@@ -9467,7 +9523,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="53">
         <v>7</v>
       </c>
@@ -9481,7 +9537,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="53">
         <v>8</v>
       </c>
@@ -9495,7 +9551,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="53">
         <v>9</v>
       </c>
@@ -9509,7 +9565,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="53">
         <v>10</v>
       </c>
@@ -9523,19 +9579,26 @@
         <v>420</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
+        <v>539</v>
+      </c>
       <c r="B40" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
+      <c r="C40" s="50" t="s">
+        <v>541</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>542</v>
+      </c>
       <c r="E40" s="50"/>
       <c r="F40" s="50"/>
       <c r="G40" s="50"/>
     </row>
-    <row r="41" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="51" t="s">
         <v>424</v>
       </c>
@@ -9552,7 +9615,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="50" t="s">
         <v>421</v>
       </c>
@@ -9562,54 +9625,62 @@
       <c r="F42" s="50"/>
       <c r="G42" s="50"/>
     </row>
-    <row r="43" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="50"/>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
       <c r="G43" s="50"/>
     </row>
-    <row r="44" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="50"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
       <c r="G44" s="50"/>
     </row>
-    <row r="45" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="50"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
       <c r="G45" s="50"/>
     </row>
-    <row r="46" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="50"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
       <c r="G46" s="50"/>
     </row>
-    <row r="47" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="44" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="63"/>
-    </row>
-    <row r="49" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="48" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="56" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="50" t="s">
+        <v>539</v>
+      </c>
+      <c r="B49" s="73" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="50" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="11" t="s">
         <v>242</v>
       </c>
@@ -9620,106 +9691,115 @@
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2">
         <v>1</v>
       </c>
-      <c r="C51" s="60" t="s">
+      <c r="C51" s="71" t="s">
         <v>425</v>
       </c>
       <c r="D51" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="2">
         <v>2</v>
       </c>
-      <c r="C52" s="60"/>
+      <c r="C52" s="71"/>
       <c r="D52" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2">
         <v>3</v>
       </c>
-      <c r="C53" s="60"/>
+      <c r="C53" s="71"/>
       <c r="D53" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
         <v>4</v>
       </c>
-      <c r="C54" s="60"/>
+      <c r="C54" s="71"/>
       <c r="D54" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="2">
         <v>5</v>
       </c>
-      <c r="C55" s="60"/>
+      <c r="C55" s="71"/>
       <c r="D55" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
         <v>6</v>
       </c>
-      <c r="C56" s="60"/>
+      <c r="C56" s="71"/>
       <c r="D56" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2">
         <v>7</v>
       </c>
-      <c r="C57" s="60"/>
+      <c r="C57" s="71"/>
       <c r="D57" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
         <v>8</v>
       </c>
-      <c r="C58" s="60"/>
+      <c r="C58" s="71"/>
       <c r="D58" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="2">
         <v>9</v>
       </c>
-      <c r="C59" s="60"/>
+      <c r="C59" s="71"/>
       <c r="D59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
         <v>10</v>
       </c>
-      <c r="C60" s="60"/>
+      <c r="C60" s="71"/>
       <c r="D60" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="50" t="s">
+        <v>539</v>
+      </c>
+      <c r="B63" s="73" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="64" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="50" t="s">
+        <v>547</v>
+      </c>
+      <c r="F63" s="50" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="41" t="s">
         <v>249</v>
       </c>
@@ -9736,42 +9816,45 @@
         <v>253</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="C65" s="61" t="s">
-        <v>437</v>
-      </c>
-      <c r="D65" s="62"/>
-      <c r="E65" s="62"/>
-      <c r="F65" s="62"/>
-    </row>
-    <row r="66" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="59"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-    </row>
-    <row r="67" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="59"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="59"/>
-    </row>
-    <row r="68" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="59"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="59"/>
-    </row>
-    <row r="69" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C65" s="67" t="s">
+        <v>545</v>
+      </c>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+    </row>
+    <row r="66" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="69"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+    </row>
+    <row r="67" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="69"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="69"/>
+      <c r="F67" s="69"/>
+    </row>
+    <row r="68" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="69"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="69"/>
+    </row>
+    <row r="69" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="50" t="s">
+        <v>538</v>
+      </c>
+      <c r="B70" s="73" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="11" t="s">
         <v>255</v>
       </c>
@@ -9782,70 +9865,73 @@
         <v>257</v>
       </c>
     </row>
-    <row r="72" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
         <v>1</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D72" s="2">
         <v>147258369</v>
       </c>
     </row>
-    <row r="73" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2">
         <v>2</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D73" s="2">
         <v>247258369</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
         <v>3</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D74" s="2">
         <v>347258369</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2">
         <v>4</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D75" s="2">
         <v>447258369</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="2">
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D76" s="2">
         <v>547258369</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="48" t="s">
+    <row r="77" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="50" t="s">
+        <v>538</v>
+      </c>
+      <c r="B79" s="73" t="s">
         <v>260</v>
       </c>
       <c r="C79" s="50"/>
     </row>
-    <row r="80" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="11" t="s">
         <v>261</v>
       </c>
@@ -9883,7 +9969,7 @@
         <v>3</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D83" s="2">
         <v>1</v>
@@ -9894,7 +9980,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D84" s="2">
         <v>1</v>
@@ -9905,7 +9991,7 @@
         <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -9916,7 +10002,7 @@
         <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -9927,7 +10013,7 @@
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D87" s="2">
         <v>1</v>
@@ -9949,18 +10035,18 @@
       </c>
     </row>
     <row r="92" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="61" t="s">
-        <v>439</v>
-      </c>
-      <c r="C92" s="62"/>
+      <c r="B92" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="C92" s="68"/>
     </row>
     <row r="93" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="59"/>
-      <c r="C93" s="59"/>
+      <c r="B93" s="69"/>
+      <c r="C93" s="69"/>
     </row>
     <row r="94" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="59"/>
-      <c r="C94" s="59"/>
+      <c r="B94" s="69"/>
+      <c r="C94" s="69"/>
     </row>
     <row r="95" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9969,13 +10055,13 @@
         <v>275</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G97" s="50" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="98" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10002,8 +10088,8 @@
       <c r="B99" s="53">
         <v>1</v>
       </c>
-      <c r="C99" s="64" t="s">
-        <v>440</v>
+      <c r="C99" s="57" t="s">
+        <v>437</v>
       </c>
       <c r="D99" s="53">
         <v>1</v>
@@ -10019,8 +10105,8 @@
       <c r="B100" s="53">
         <v>2</v>
       </c>
-      <c r="C100" s="64" t="s">
-        <v>442</v>
+      <c r="C100" s="57" t="s">
+        <v>439</v>
       </c>
       <c r="D100" s="53">
         <v>2</v>
@@ -10036,8 +10122,8 @@
       <c r="B101" s="53">
         <v>3</v>
       </c>
-      <c r="C101" s="64" t="s">
-        <v>444</v>
+      <c r="C101" s="57" t="s">
+        <v>441</v>
       </c>
       <c r="D101" s="53">
         <v>3</v>
@@ -10053,8 +10139,8 @@
       <c r="B102" s="53">
         <v>4</v>
       </c>
-      <c r="C102" s="64" t="s">
-        <v>446</v>
+      <c r="C102" s="57" t="s">
+        <v>443</v>
       </c>
       <c r="D102" s="53">
         <v>4</v>
@@ -10070,8 +10156,8 @@
       <c r="B103" s="53">
         <v>5</v>
       </c>
-      <c r="C103" s="64" t="s">
-        <v>448</v>
+      <c r="C103" s="57" t="s">
+        <v>445</v>
       </c>
       <c r="D103" s="53">
         <v>5</v>
@@ -10087,8 +10173,8 @@
       <c r="B104" s="53">
         <v>6</v>
       </c>
-      <c r="C104" s="64" t="s">
-        <v>442</v>
+      <c r="C104" s="57" t="s">
+        <v>439</v>
       </c>
       <c r="D104" s="53">
         <v>6</v>
@@ -10104,8 +10190,8 @@
       <c r="B105" s="53">
         <v>7</v>
       </c>
-      <c r="C105" s="64" t="s">
-        <v>444</v>
+      <c r="C105" s="57" t="s">
+        <v>441</v>
       </c>
       <c r="D105" s="53">
         <v>7</v>
@@ -10121,8 +10207,8 @@
       <c r="B106" s="53">
         <v>8</v>
       </c>
-      <c r="C106" s="64" t="s">
-        <v>448</v>
+      <c r="C106" s="57" t="s">
+        <v>445</v>
       </c>
       <c r="D106" s="53">
         <v>8</v>
@@ -10138,8 +10224,8 @@
       <c r="B107" s="53">
         <v>9</v>
       </c>
-      <c r="C107" s="64" t="s">
-        <v>448</v>
+      <c r="C107" s="57" t="s">
+        <v>445</v>
       </c>
       <c r="D107" s="53">
         <v>9</v>
@@ -10155,8 +10241,8 @@
       <c r="B108" s="53">
         <v>10</v>
       </c>
-      <c r="C108" s="64" t="s">
-        <v>448</v>
+      <c r="C108" s="57" t="s">
+        <v>445</v>
       </c>
       <c r="D108" s="53">
         <v>10</v>
@@ -10172,8 +10258,8 @@
       <c r="B109" s="53">
         <v>11</v>
       </c>
-      <c r="C109" s="64" t="s">
-        <v>455</v>
+      <c r="C109" s="57" t="s">
+        <v>452</v>
       </c>
       <c r="D109" s="53">
         <v>11</v>
@@ -10189,8 +10275,8 @@
       <c r="B110" s="53">
         <v>12</v>
       </c>
-      <c r="C110" s="64" t="s">
-        <v>456</v>
+      <c r="C110" s="57" t="s">
+        <v>453</v>
       </c>
       <c r="D110" s="53">
         <v>12</v>
@@ -10206,8 +10292,8 @@
       <c r="B111" s="53">
         <v>13</v>
       </c>
-      <c r="C111" s="64" t="s">
-        <v>457</v>
+      <c r="C111" s="57" t="s">
+        <v>454</v>
       </c>
       <c r="D111" s="53">
         <v>13</v>
@@ -10226,7 +10312,7 @@
         <v>300</v>
       </c>
       <c r="E114" s="50" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="115" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10247,27 +10333,27 @@
       </c>
     </row>
     <row r="116" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="61" t="s">
-        <v>462</v>
-      </c>
-      <c r="C116" s="62"/>
-      <c r="D116" s="62"/>
-      <c r="E116" s="62"/>
-      <c r="F116" s="62"/>
+      <c r="B116" s="67" t="s">
+        <v>459</v>
+      </c>
+      <c r="C116" s="68"/>
+      <c r="D116" s="68"/>
+      <c r="E116" s="68"/>
+      <c r="F116" s="68"/>
     </row>
     <row r="117" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="59"/>
-      <c r="C117" s="59"/>
-      <c r="D117" s="59"/>
-      <c r="E117" s="59"/>
-      <c r="F117" s="59"/>
+      <c r="B117" s="69"/>
+      <c r="C117" s="69"/>
+      <c r="D117" s="69"/>
+      <c r="E117" s="69"/>
+      <c r="F117" s="69"/>
     </row>
     <row r="118" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="59"/>
-      <c r="C118" s="59"/>
-      <c r="D118" s="59"/>
-      <c r="E118" s="59"/>
-      <c r="F118" s="59"/>
+      <c r="B118" s="69"/>
+      <c r="C118" s="69"/>
+      <c r="D118" s="69"/>
+      <c r="E118" s="69"/>
+      <c r="F118" s="69"/>
     </row>
     <row r="119" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10297,7 +10383,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="53" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="125" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10313,7 +10399,7 @@
         <v>4</v>
       </c>
       <c r="C126" s="53" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="127" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10335,11 +10421,11 @@
       </c>
     </row>
     <row r="131" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="65" t="s">
-        <v>465</v>
-      </c>
-      <c r="C131" s="66"/>
-      <c r="D131" s="67"/>
+      <c r="B131" s="64" t="s">
+        <v>462</v>
+      </c>
+      <c r="C131" s="65"/>
+      <c r="D131" s="66"/>
     </row>
     <row r="132" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="53">
@@ -10724,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="53" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="170" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10732,7 +10818,7 @@
         <v>2</v>
       </c>
       <c r="C170" s="53" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="171" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10740,7 +10826,7 @@
         <v>3</v>
       </c>
       <c r="C171" s="53" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="172" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10748,7 +10834,7 @@
         <v>4</v>
       </c>
       <c r="C172" s="53" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="173" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10756,7 +10842,7 @@
         <v>5</v>
       </c>
       <c r="C173" s="53" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10764,7 +10850,7 @@
         <v>6</v>
       </c>
       <c r="C174" s="53" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="175" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10772,7 +10858,7 @@
         <v>7</v>
       </c>
       <c r="C175" s="53" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="176" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10797,60 +10883,60 @@
       </c>
     </row>
     <row r="180" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="68" t="s">
-        <v>473</v>
+      <c r="B180" s="58" t="s">
+        <v>470</v>
       </c>
       <c r="C180" s="50"/>
       <c r="D180" s="50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E180" s="50" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="181" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="68" t="s">
-        <v>476</v>
+      <c r="B181" s="58" t="s">
+        <v>473</v>
       </c>
       <c r="C181" s="50"/>
       <c r="D181" s="50" t="s">
-        <v>477</v>
-      </c>
-      <c r="E181" s="69" t="s">
-        <v>478</v>
+        <v>474</v>
+      </c>
+      <c r="E181" s="59" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="182" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="68" t="s">
-        <v>479</v>
+      <c r="B182" s="58" t="s">
+        <v>476</v>
       </c>
       <c r="C182" s="50"/>
       <c r="D182" s="50" t="s">
-        <v>480</v>
-      </c>
-      <c r="E182" s="69" t="s">
+        <v>477</v>
+      </c>
+      <c r="E182" s="59" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="183" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="58" t="s">
         <v>478</v>
-      </c>
-    </row>
-    <row r="183" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="68" t="s">
-        <v>481</v>
       </c>
       <c r="C183" s="50"/>
       <c r="D183" s="50" t="s">
-        <v>482</v>
-      </c>
-      <c r="E183" s="69" t="s">
-        <v>478</v>
+        <v>479</v>
+      </c>
+      <c r="E183" s="59" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="184" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="68" t="s">
-        <v>483</v>
+      <c r="B184" s="58" t="s">
+        <v>480</v>
       </c>
       <c r="C184" s="50"/>
       <c r="D184" s="50" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E184" s="50"/>
     </row>
@@ -10884,7 +10970,7 @@
       <c r="H189" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="J189" s="48" t="s">
+      <c r="J189" s="73" t="s">
         <v>322</v>
       </c>
     </row>
@@ -10893,22 +10979,22 @@
         <v>1</v>
       </c>
       <c r="C190" s="53" t="s">
-        <v>485</v>
-      </c>
-      <c r="D190" s="64" t="s">
-        <v>486</v>
+        <v>482</v>
+      </c>
+      <c r="D190" s="57" t="s">
+        <v>483</v>
       </c>
       <c r="E190" s="53" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F190" s="53">
         <v>123456789</v>
       </c>
-      <c r="G190" s="70" t="s">
-        <v>488</v>
+      <c r="G190" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H190" s="53" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J190" s="11" t="s">
         <v>323</v>
@@ -10922,28 +11008,28 @@
         <v>2</v>
       </c>
       <c r="C191" s="53" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D191" s="53" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E191" s="53" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F191" s="53">
         <v>123456789</v>
       </c>
-      <c r="G191" s="70" t="s">
+      <c r="G191" s="60" t="s">
+        <v>485</v>
+      </c>
+      <c r="H191" s="53" t="s">
         <v>488</v>
-      </c>
-      <c r="H191" s="53" t="s">
-        <v>491</v>
       </c>
       <c r="J191" s="53">
         <v>1</v>
       </c>
       <c r="K191" s="53" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="192" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10951,28 +11037,28 @@
         <v>3</v>
       </c>
       <c r="C192" s="53" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D192" s="53" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E192" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F192" s="53">
         <v>123456789</v>
       </c>
-      <c r="G192" s="70" t="s">
-        <v>488</v>
+      <c r="G192" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H192" s="53" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J192" s="53">
         <v>2</v>
       </c>
       <c r="K192" s="53" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
     </row>
     <row r="193" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10980,28 +11066,28 @@
         <v>4</v>
       </c>
       <c r="C193" s="53" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D193" s="53" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E193" s="53" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F193" s="53">
         <v>123456789</v>
       </c>
-      <c r="G193" s="70" t="s">
-        <v>488</v>
+      <c r="G193" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H193" s="53" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J193" s="53">
         <v>3</v>
       </c>
       <c r="K193" s="53" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
     </row>
     <row r="194" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11009,28 +11095,28 @@
         <v>5</v>
       </c>
       <c r="C194" s="53" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D194" s="53" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E194" s="53" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F194" s="53">
         <v>123456789</v>
       </c>
-      <c r="G194" s="70" t="s">
-        <v>488</v>
+      <c r="G194" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H194" s="53" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J194" s="53">
         <v>4</v>
       </c>
       <c r="K194" s="53" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
     </row>
     <row r="195" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11038,22 +11124,22 @@
         <v>6</v>
       </c>
       <c r="C195" s="53" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D195" s="53" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E195" s="53" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F195" s="53">
         <v>123456789</v>
       </c>
-      <c r="G195" s="70" t="s">
-        <v>488</v>
+      <c r="G195" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H195" s="53" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="196" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11061,22 +11147,22 @@
         <v>7</v>
       </c>
       <c r="C196" s="53" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D196" s="53" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E196" s="53" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F196" s="53">
         <v>123456789</v>
       </c>
-      <c r="G196" s="70" t="s">
-        <v>488</v>
+      <c r="G196" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H196" s="53" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="197" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11084,22 +11170,22 @@
         <v>8</v>
       </c>
       <c r="C197" s="53" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D197" s="53" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E197" s="53" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F197" s="53">
         <v>123456789</v>
       </c>
-      <c r="G197" s="70" t="s">
-        <v>488</v>
+      <c r="G197" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H197" s="53" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="198" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11107,22 +11193,22 @@
         <v>9</v>
       </c>
       <c r="C198" s="53" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D198" s="53" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E198" s="53" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F198" s="53">
         <v>123456789</v>
       </c>
-      <c r="G198" s="70" t="s">
-        <v>488</v>
+      <c r="G198" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H198" s="53" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="199" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11130,30 +11216,37 @@
         <v>10</v>
       </c>
       <c r="C199" s="53" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D199" s="53" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E199" s="53" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F199" s="53">
         <v>123456789</v>
       </c>
-      <c r="G199" s="70" t="s">
-        <v>488</v>
+      <c r="G199" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H199" s="53" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="200" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I201" s="50" t="s">
+        <v>550</v>
+      </c>
+    </row>
     <row r="202" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B202" s="48" t="s">
         <v>314</v>
       </c>
+      <c r="I202" s="72" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="203" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B203" s="11" t="s">
@@ -11186,22 +11279,22 @@
         <v>1</v>
       </c>
       <c r="C204" s="53" t="s">
-        <v>474</v>
-      </c>
-      <c r="D204" s="64" t="s">
-        <v>534</v>
+        <v>471</v>
+      </c>
+      <c r="D204" s="57" t="s">
+        <v>551</v>
       </c>
       <c r="E204" s="53" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F204" s="53">
         <v>123456789</v>
       </c>
-      <c r="G204" s="70" t="s">
-        <v>488</v>
+      <c r="G204" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H204" s="53" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="I204" s="53">
         <v>1</v>
@@ -11212,22 +11305,22 @@
         <v>2</v>
       </c>
       <c r="C205" s="53" t="s">
-        <v>533</v>
-      </c>
-      <c r="D205" s="53" t="s">
-        <v>532</v>
+        <v>521</v>
+      </c>
+      <c r="D205" s="75" t="s">
+        <v>552</v>
       </c>
       <c r="E205" s="53" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F205" s="53">
         <v>123456789</v>
       </c>
-      <c r="G205" s="70" t="s">
-        <v>488</v>
+      <c r="G205" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H205" s="53" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="I205" s="53">
         <v>1</v>
@@ -11238,22 +11331,22 @@
         <v>3</v>
       </c>
       <c r="C206" s="53" t="s">
-        <v>531</v>
-      </c>
-      <c r="D206" s="64" t="s">
-        <v>530</v>
+        <v>520</v>
+      </c>
+      <c r="D206" s="57" t="s">
+        <v>551</v>
       </c>
       <c r="E206" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F206" s="53">
         <v>123456789</v>
       </c>
-      <c r="G206" s="70" t="s">
-        <v>488</v>
+      <c r="G206" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H206" s="53" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="I206" s="53">
         <v>2</v>
@@ -11264,22 +11357,22 @@
         <v>4</v>
       </c>
       <c r="C207" s="53" t="s">
-        <v>529</v>
-      </c>
-      <c r="D207" s="53" t="s">
-        <v>528</v>
+        <v>519</v>
+      </c>
+      <c r="D207" s="75" t="s">
+        <v>552</v>
       </c>
       <c r="E207" s="53" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F207" s="53">
         <v>123456789</v>
       </c>
-      <c r="G207" s="70" t="s">
-        <v>488</v>
+      <c r="G207" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H207" s="53" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="I207" s="53">
         <v>1</v>
@@ -11290,22 +11383,22 @@
         <v>5</v>
       </c>
       <c r="C208" s="53" t="s">
-        <v>527</v>
-      </c>
-      <c r="D208" s="64" t="s">
-        <v>526</v>
+        <v>518</v>
+      </c>
+      <c r="D208" s="57" t="s">
+        <v>551</v>
       </c>
       <c r="E208" s="53" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F208" s="53">
         <v>123456789</v>
       </c>
-      <c r="G208" s="70" t="s">
-        <v>488</v>
+      <c r="G208" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H208" s="53" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="I208" s="53">
         <v>1</v>
@@ -11316,22 +11409,22 @@
         <v>6</v>
       </c>
       <c r="C209" s="53" t="s">
-        <v>525</v>
-      </c>
-      <c r="D209" s="53" t="s">
-        <v>524</v>
+        <v>517</v>
+      </c>
+      <c r="D209" s="75" t="s">
+        <v>552</v>
       </c>
       <c r="E209" s="53" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F209" s="53">
         <v>123456789</v>
       </c>
-      <c r="G209" s="70" t="s">
-        <v>488</v>
+      <c r="G209" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H209" s="53" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="I209" s="53">
         <v>1</v>
@@ -11342,22 +11435,22 @@
         <v>7</v>
       </c>
       <c r="C210" s="53" t="s">
-        <v>523</v>
-      </c>
-      <c r="D210" s="64" t="s">
-        <v>522</v>
+        <v>516</v>
+      </c>
+      <c r="D210" s="57" t="s">
+        <v>551</v>
       </c>
       <c r="E210" s="53" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F210" s="53">
         <v>123456789</v>
       </c>
-      <c r="G210" s="70" t="s">
-        <v>488</v>
+      <c r="G210" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H210" s="53" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="I210" s="53">
         <v>2</v>
@@ -11368,22 +11461,22 @@
         <v>8</v>
       </c>
       <c r="C211" s="53" t="s">
-        <v>521</v>
-      </c>
-      <c r="D211" s="53" t="s">
-        <v>520</v>
+        <v>515</v>
+      </c>
+      <c r="D211" s="75" t="s">
+        <v>552</v>
       </c>
       <c r="E211" s="53" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F211" s="53">
         <v>123456789</v>
       </c>
-      <c r="G211" s="70" t="s">
-        <v>488</v>
+      <c r="G211" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H211" s="53" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="I211" s="53">
         <v>3</v>
@@ -11394,22 +11487,22 @@
         <v>9</v>
       </c>
       <c r="C212" s="53" t="s">
-        <v>519</v>
-      </c>
-      <c r="D212" s="64" t="s">
-        <v>518</v>
+        <v>514</v>
+      </c>
+      <c r="D212" s="57" t="s">
+        <v>551</v>
       </c>
       <c r="E212" s="53" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F212" s="53">
         <v>123456789</v>
       </c>
-      <c r="G212" s="70" t="s">
-        <v>488</v>
+      <c r="G212" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H212" s="53" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="I212" s="53">
         <v>1</v>
@@ -11420,22 +11513,22 @@
         <v>10</v>
       </c>
       <c r="C213" s="53" t="s">
-        <v>517</v>
-      </c>
-      <c r="D213" s="53" t="s">
-        <v>516</v>
+        <v>513</v>
+      </c>
+      <c r="D213" s="75" t="s">
+        <v>552</v>
       </c>
       <c r="E213" s="53" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F213" s="53">
         <v>123456789</v>
       </c>
-      <c r="G213" s="70" t="s">
-        <v>488</v>
+      <c r="G213" s="60" t="s">
+        <v>485</v>
       </c>
       <c r="H213" s="53" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="I213" s="53">
         <v>4</v>
@@ -11466,27 +11559,27 @@
       </c>
     </row>
     <row r="218" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="61" t="s">
-        <v>545</v>
-      </c>
-      <c r="C218" s="62"/>
-      <c r="D218" s="62"/>
-      <c r="E218" s="62"/>
-      <c r="F218" s="62"/>
+      <c r="B218" s="67" t="s">
+        <v>532</v>
+      </c>
+      <c r="C218" s="68"/>
+      <c r="D218" s="68"/>
+      <c r="E218" s="68"/>
+      <c r="F218" s="68"/>
     </row>
     <row r="219" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="59"/>
-      <c r="C219" s="59"/>
-      <c r="D219" s="59"/>
-      <c r="E219" s="59"/>
-      <c r="F219" s="59"/>
+      <c r="B219" s="69"/>
+      <c r="C219" s="69"/>
+      <c r="D219" s="69"/>
+      <c r="E219" s="69"/>
+      <c r="F219" s="69"/>
     </row>
     <row r="220" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="59"/>
-      <c r="C220" s="59"/>
-      <c r="D220" s="59"/>
-      <c r="E220" s="59"/>
-      <c r="F220" s="59"/>
+      <c r="B220" s="69"/>
+      <c r="C220" s="69"/>
+      <c r="D220" s="69"/>
+      <c r="E220" s="69"/>
+      <c r="F220" s="69"/>
     </row>
     <row r="221" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="222" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11523,7 +11616,7 @@
     <row r="230" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="231" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="232" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B232" s="71" t="s">
+      <c r="B232" s="61" t="s">
         <v>339</v>
       </c>
     </row>

--- a/1. Database Design/Java24 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java24 QuyenPhan Database Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23D08ED-37A7-4DD8-B3BC-B88D23C37480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3DC602-657D-4999-9A90-0C60DE39EE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="433" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1689,7 +1689,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="561">
   <si>
     <t>MatHang</t>
   </si>
@@ -3398,12 +3398,6 @@
     <t>T19</t>
   </si>
   <si>
-    <t>Sử dụng ID(s) từ T09_ORDER
-DeliveryFee = random(20,30,40,50,60)
-VoucherId = random(1, maxC19Id)
-TotalOfMoney = 0, cập nhật tính tiền xử lý sau</t>
-  </si>
-  <si>
     <t>Thẻ tín dụng</t>
   </si>
   <si>
@@ -3440,9 +3434,6 @@
     <t>Nhân viên 1</t>
   </si>
   <si>
-    <t>SYSDATE - max(STATUS_ID) - ORDER_STATUS_ID</t>
-  </si>
-  <si>
     <t>-- 2 Đơn hàng từ 6 - 8 --&gt; Đóng gói thành công (trạng thái từ 1 - 3)</t>
   </si>
   <si>
@@ -3464,9 +3455,6 @@
     <t>Nhân Viên 4</t>
   </si>
   <si>
-    <t>-- 4. Đơn hàng từ 13  --&gt; Giao hàng thất bại (trạng thái 1,2,3,4,6)</t>
-  </si>
-  <si>
     <t>Nhân Viên 5</t>
   </si>
   <si>
@@ -3618,10 +3606,6 @@
   </si>
   <si>
     <t>nv10auto</t>
-  </si>
-  <si>
-    <t>Lấy thông tin từ bảng Khách Hàng
-Người nhận + Id, SĐT 123456789, Địa Chỉ + id</t>
   </si>
   <si>
     <t>Phòng cơ sở vật chất</t>
@@ -3698,6 +3682,50 @@
   </si>
   <si>
     <t>nv2@gmail.com</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>Sử dụng ID(s) từ T09_ORDER (Ngoại trừ Đơn Hàng 11 12 bị hủy)
+DeliveryFee = random(20,30,40,50,60)
+VoucherId = random(1, maxC19Id)
+TotalOfMoney = 0, cập nhật tính tiền xử lý sau</t>
+  </si>
+  <si>
+    <t>-- 5. Đơn hàng từ 13  --&gt; Giao hàng thất bại (trạng thái 1,2,3,4,6)</t>
+  </si>
+  <si>
+    <t>SYSDATE - max(ORDER_STATUS_ID) - ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C18_RECEIVER_PHONE</t>
+  </si>
+  <si>
+    <t>Lấy thông tin từ bảng Khách Hàng, mỗi khách hàng sẽ có 1 delivery_address
+C18_RECEIVER_NAME = 'Người nhận' + Id
+C18_RECEIVER_PHONE 123456789
+C18_ADDRESS = 'Địa Chỉ' + id</t>
+  </si>
+  <si>
+    <t>Tạo 5 voucher
+2 cái: voucher cho money
+3 cái: voucher cho percent</t>
+  </si>
+  <si>
+    <t>Role 1</t>
+  </si>
+  <si>
+    <t>Role 2</t>
+  </si>
+  <si>
+    <t>Role 3</t>
+  </si>
+  <si>
+    <t>Role 4</t>
+  </si>
+  <si>
+    <t>Role 5</t>
   </si>
 </sst>
 </file>
@@ -4086,7 +4114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4232,9 +4260,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4269,6 +4294,15 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4299,17 +4333,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7591,7 +7634,7 @@
       <c r="J2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="M2" s="55" t="s">
+      <c r="M2" s="54" t="s">
         <v>423</v>
       </c>
     </row>
@@ -8344,10 +8387,10 @@
       <c r="B27" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="D27" s="63"/>
+      <c r="D27" s="65"/>
       <c r="E27" s="35"/>
       <c r="F27" s="35"/>
       <c r="G27" s="35"/>
@@ -9093,7 +9136,7 @@
   <dimension ref="A1:K1000"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="50" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="49" customWidth="1"/>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
@@ -9106,26 +9149,26 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>538</v>
-      </c>
-      <c r="B2" s="74" t="s">
+      <c r="A2" s="49" t="s">
+        <v>534</v>
+      </c>
+      <c r="B2" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50" t="s">
-        <v>537</v>
-      </c>
-      <c r="E2" s="50"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49" t="s">
+        <v>533</v>
+      </c>
+      <c r="E2" s="49"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="50" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="51" t="s">
         <v>259</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -9133,300 +9176,300 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="53">
+      <c r="B4" s="52">
         <v>1</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="52" t="s">
         <v>383</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="52">
         <v>1</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="52" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="53">
+      <c r="B5" s="52">
         <v>2</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="52" t="s">
         <v>384</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="52">
         <v>1</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="52" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="53">
+      <c r="B6" s="52">
         <v>3</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="52">
         <v>1</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="52" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="53">
+      <c r="B7" s="52">
         <v>4</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="52" t="s">
         <v>386</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="52">
         <v>2</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="52" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="53">
+      <c r="B8" s="52">
         <v>5</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="52" t="s">
         <v>387</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="52">
         <v>2</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="53">
+      <c r="B9" s="52">
         <v>6</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="52" t="s">
         <v>388</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="52">
         <v>3</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="52" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="53">
+      <c r="B10" s="52">
         <v>7</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="52" t="s">
         <v>389</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="52">
         <v>3</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="52" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="53">
+      <c r="B11" s="52">
         <v>8</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="52" t="s">
         <v>390</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="52">
         <v>3</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="52" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="53">
+      <c r="B12" s="52">
         <v>9</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="52">
         <v>3</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="52" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="53">
+      <c r="B13" s="52">
         <v>10</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="52" t="s">
         <v>392</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="52">
         <v>3</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="52" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="53">
+      <c r="B14" s="52">
         <v>11</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="52">
         <v>4</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" s="52" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <v>12</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="52" t="s">
         <v>394</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="52">
         <v>1</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="52" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="53">
+      <c r="B16" s="52">
         <v>13</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="52" t="s">
         <v>395</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="52">
         <v>4</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="52" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="53">
+      <c r="B17" s="52">
         <v>14</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="52" t="s">
         <v>396</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="52">
         <v>5</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="52" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="53">
+      <c r="B18" s="52">
         <v>15</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="52" t="s">
         <v>397</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="52">
         <v>5</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="52" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="53">
+      <c r="B19" s="52">
         <v>16</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="52">
         <v>6</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="E19" s="52" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="53">
+      <c r="B20" s="52">
         <v>17</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="52">
         <v>6</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="52" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="53">
+      <c r="B21" s="52">
         <v>18</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="52" t="s">
         <v>400</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="52">
         <v>5</v>
       </c>
-      <c r="E21" s="53" t="s">
+      <c r="E21" s="52" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="53">
+      <c r="B22" s="52">
         <v>19</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="52" t="s">
         <v>401</v>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="52">
         <v>7</v>
       </c>
-      <c r="E22" s="53" t="s">
+      <c r="E22" s="52" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="53">
+      <c r="B23" s="52">
         <v>20</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="52" t="s">
         <v>402</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="52">
         <v>7</v>
       </c>
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="52" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50" t="s">
-        <v>540</v>
-      </c>
-      <c r="B26" s="74" t="s">
+      <c r="A26" s="49" t="s">
+        <v>536</v>
+      </c>
+      <c r="B26" s="63" t="s">
         <v>218</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
     </row>
     <row r="27" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>219</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -9440,172 +9483,172 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="53">
+      <c r="B28" s="52">
         <v>1</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="53">
+      <c r="D28" s="52">
         <v>0</v>
       </c>
-      <c r="E28" s="53" t="s">
+      <c r="E28" s="52" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="53">
+      <c r="B29" s="52">
         <v>2</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="53">
+      <c r="D29" s="52">
         <v>0</v>
       </c>
-      <c r="E29" s="53" t="s">
+      <c r="E29" s="52" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="53">
+      <c r="B30" s="52">
         <v>3</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="52">
         <v>0</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="52" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="53">
+      <c r="B31" s="52">
         <v>4</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="53">
+      <c r="D31" s="52">
         <v>0</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="52" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="53">
+      <c r="B32" s="52">
         <v>5</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="D32" s="53">
+      <c r="D32" s="52">
         <v>0</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="52" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="53">
+      <c r="B33" s="52">
         <v>6</v>
       </c>
-      <c r="C33" s="53" t="s">
+      <c r="C33" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="53">
+      <c r="D33" s="52">
         <v>1</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="52" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="53">
+      <c r="B34" s="52">
         <v>7</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="53">
+      <c r="D34" s="52">
         <v>1</v>
       </c>
-      <c r="E34" s="53" t="s">
+      <c r="E34" s="52" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="53">
+      <c r="B35" s="52">
         <v>8</v>
       </c>
-      <c r="C35" s="53" t="s">
+      <c r="C35" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="53">
+      <c r="D35" s="52">
         <v>1</v>
       </c>
-      <c r="E35" s="53" t="s">
+      <c r="E35" s="52" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="53">
+      <c r="B36" s="52">
         <v>9</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="D36" s="53">
+      <c r="D36" s="52">
         <v>1</v>
       </c>
-      <c r="E36" s="53" t="s">
+      <c r="E36" s="52" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="53">
+      <c r="B37" s="52">
         <v>10</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C37" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="D37" s="53">
+      <c r="D37" s="52">
         <v>1</v>
       </c>
-      <c r="E37" s="53" t="s">
+      <c r="E37" s="52" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="50" t="s">
-        <v>539</v>
-      </c>
-      <c r="B40" s="49" t="s">
+      <c r="A40" s="49" t="s">
+        <v>535</v>
+      </c>
+      <c r="B40" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="C40" s="50" t="s">
-        <v>541</v>
-      </c>
-      <c r="D40" s="50" t="s">
-        <v>542</v>
-      </c>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
+      <c r="C40" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="D40" s="49" t="s">
+        <v>538</v>
+      </c>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="51" t="s">
+      <c r="B41" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="D41" s="54" t="s">
+      <c r="D41" s="53" t="s">
         <v>239</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -9616,68 +9659,68 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="50"/>
-      <c r="C43" s="70" t="s">
+      <c r="B43" s="49"/>
+      <c r="C43" s="72" t="s">
         <v>422</v>
       </c>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="50"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="49"/>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="50"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="50"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="49"/>
     </row>
     <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="50"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="50"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="49"/>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="50"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="50"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="49"/>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="44" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="56" t="s">
-        <v>544</v>
+      <c r="D48" s="55" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="50" t="s">
-        <v>539</v>
-      </c>
-      <c r="B49" s="73" t="s">
+      <c r="A49" s="49" t="s">
+        <v>535</v>
+      </c>
+      <c r="B49" s="62" t="s">
         <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -9695,7 +9738,7 @@
       <c r="B51" s="2">
         <v>1</v>
       </c>
-      <c r="C51" s="71" t="s">
+      <c r="C51" s="73" t="s">
         <v>425</v>
       </c>
       <c r="D51" s="2">
@@ -9706,7 +9749,7 @@
       <c r="B52" s="2">
         <v>2</v>
       </c>
-      <c r="C52" s="71"/>
+      <c r="C52" s="73"/>
       <c r="D52" s="2">
         <v>2</v>
       </c>
@@ -9715,7 +9758,7 @@
       <c r="B53" s="2">
         <v>3</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="73"/>
       <c r="D53" s="2">
         <v>3</v>
       </c>
@@ -9724,7 +9767,7 @@
       <c r="B54" s="2">
         <v>4</v>
       </c>
-      <c r="C54" s="71"/>
+      <c r="C54" s="73"/>
       <c r="D54" s="2">
         <v>4</v>
       </c>
@@ -9733,7 +9776,7 @@
       <c r="B55" s="2">
         <v>5</v>
       </c>
-      <c r="C55" s="71"/>
+      <c r="C55" s="73"/>
       <c r="D55" s="2">
         <v>5</v>
       </c>
@@ -9742,7 +9785,7 @@
       <c r="B56" s="2">
         <v>6</v>
       </c>
-      <c r="C56" s="71"/>
+      <c r="C56" s="73"/>
       <c r="D56" s="2">
         <v>6</v>
       </c>
@@ -9751,7 +9794,7 @@
       <c r="B57" s="2">
         <v>7</v>
       </c>
-      <c r="C57" s="71"/>
+      <c r="C57" s="73"/>
       <c r="D57" s="2">
         <v>7</v>
       </c>
@@ -9760,7 +9803,7 @@
       <c r="B58" s="2">
         <v>8</v>
       </c>
-      <c r="C58" s="71"/>
+      <c r="C58" s="73"/>
       <c r="D58" s="2">
         <v>8</v>
       </c>
@@ -9769,7 +9812,7 @@
       <c r="B59" s="2">
         <v>9</v>
       </c>
-      <c r="C59" s="71"/>
+      <c r="C59" s="73"/>
       <c r="D59" s="2">
         <v>9</v>
       </c>
@@ -9778,7 +9821,7 @@
       <c r="B60" s="2">
         <v>10</v>
       </c>
-      <c r="C60" s="71"/>
+      <c r="C60" s="73"/>
       <c r="D60" s="2">
         <v>10</v>
       </c>
@@ -9786,17 +9829,17 @@
     <row r="61" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="50" t="s">
-        <v>539</v>
-      </c>
-      <c r="B63" s="73" t="s">
+      <c r="A63" s="49" t="s">
+        <v>535</v>
+      </c>
+      <c r="B63" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="C63" s="50" t="s">
-        <v>547</v>
-      </c>
-      <c r="F63" s="50" t="s">
-        <v>546</v>
+      <c r="C63" s="49" t="s">
+        <v>543</v>
+      </c>
+      <c r="F63" s="49" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -9817,40 +9860,40 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="50" t="s">
+      <c r="B65" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C65" s="67" t="s">
-        <v>545</v>
-      </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
+      <c r="C65" s="69" t="s">
+        <v>541</v>
+      </c>
+      <c r="D65" s="70"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="70"/>
     </row>
     <row r="66" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="69"/>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
+      <c r="C66" s="71"/>
+      <c r="D66" s="71"/>
+      <c r="E66" s="71"/>
+      <c r="F66" s="71"/>
     </row>
     <row r="67" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="69"/>
-      <c r="D67" s="69"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
     </row>
     <row r="68" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="69"/>
-      <c r="D68" s="69"/>
-      <c r="E68" s="69"/>
-      <c r="F68" s="69"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
     </row>
     <row r="69" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="70" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="50" t="s">
-        <v>538</v>
-      </c>
-      <c r="B70" s="73" t="s">
+      <c r="A70" s="49" t="s">
+        <v>534</v>
+      </c>
+      <c r="B70" s="62" t="s">
         <v>254</v>
       </c>
     </row>
@@ -9923,13 +9966,13 @@
     <row r="77" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
-        <v>538</v>
-      </c>
-      <c r="B79" s="73" t="s">
+      <c r="A79" s="49" t="s">
+        <v>534</v>
+      </c>
+      <c r="B79" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="C79" s="50"/>
+      <c r="C79" s="49"/>
     </row>
     <row r="80" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="11" t="s">
@@ -9942,7 +9985,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="2">
         <v>1</v>
       </c>
@@ -9953,7 +9996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
         <v>2</v>
       </c>
@@ -9964,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="2">
         <v>3</v>
       </c>
@@ -9975,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
         <v>4</v>
       </c>
@@ -9986,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="2">
         <v>5</v>
       </c>
@@ -9997,7 +10040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="2">
         <v>6</v>
       </c>
@@ -10008,7 +10051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="2">
         <v>7</v>
       </c>
@@ -10019,14 +10062,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="49" t="s">
+        <v>535</v>
+      </c>
       <c r="B90" s="48" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="11" t="s">
         <v>268</v>
       </c>
@@ -10034,37 +10080,43 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="67" t="s">
+    <row r="92" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="69" t="s">
         <v>436</v>
       </c>
-      <c r="C92" s="68"/>
-    </row>
-    <row r="93" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="69"/>
-      <c r="C93" s="69"/>
-    </row>
-    <row r="94" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="69"/>
-      <c r="C94" s="69"/>
-    </row>
-    <row r="95" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="70"/>
+    </row>
+    <row r="93" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="71"/>
+      <c r="C93" s="71"/>
+    </row>
+    <row r="94" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="71"/>
+      <c r="C94" s="71"/>
+    </row>
+    <row r="95" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="49" t="s">
+        <v>534</v>
+      </c>
       <c r="B97" s="48" t="s">
         <v>275</v>
       </c>
-      <c r="E97" s="50" t="s">
+      <c r="D97" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="E97" s="49" t="s">
         <v>455</v>
       </c>
-      <c r="F97" s="50" t="s">
+      <c r="F97" s="49" t="s">
         <v>456</v>
       </c>
-      <c r="G97" s="50" t="s">
+      <c r="G97" s="49" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="98" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="11" t="s">
         <v>276</v>
       </c>
@@ -10084,238 +10136,280 @@
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="53">
+    <row r="99" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="52">
         <v>1</v>
       </c>
-      <c r="C99" s="57" t="s">
+      <c r="C99" s="56" t="s">
         <v>437</v>
       </c>
-      <c r="D99" s="53">
+      <c r="D99" s="52">
         <v>1</v>
       </c>
-      <c r="E99" s="53">
+      <c r="E99" s="52">
         <v>1</v>
       </c>
-      <c r="F99" s="53">
+      <c r="F99" s="52">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="53">
+      <c r="G99" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="52">
         <v>2</v>
       </c>
-      <c r="C100" s="57" t="s">
+      <c r="C100" s="56" t="s">
         <v>439</v>
       </c>
-      <c r="D100" s="53">
+      <c r="D100" s="52">
         <v>2</v>
       </c>
-      <c r="E100" s="53">
+      <c r="E100" s="52">
         <v>2</v>
       </c>
-      <c r="F100" s="53">
+      <c r="F100" s="52">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="53">
+      <c r="G100" s="74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="52">
         <v>3</v>
       </c>
-      <c r="C101" s="57" t="s">
+      <c r="C101" s="56" t="s">
         <v>441</v>
       </c>
-      <c r="D101" s="53">
+      <c r="D101" s="52">
         <v>3</v>
       </c>
-      <c r="E101" s="53">
+      <c r="E101" s="52">
         <v>3</v>
       </c>
-      <c r="F101" s="53">
+      <c r="F101" s="52">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="53">
+      <c r="G101" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="52">
         <v>4</v>
       </c>
-      <c r="C102" s="57" t="s">
+      <c r="C102" s="56" t="s">
         <v>443</v>
       </c>
-      <c r="D102" s="53">
+      <c r="D102" s="52">
         <v>4</v>
       </c>
-      <c r="E102" s="53">
+      <c r="E102" s="52">
         <v>4</v>
       </c>
-      <c r="F102" s="53">
+      <c r="F102" s="52">
         <v>4</v>
       </c>
-    </row>
-    <row r="103" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="53">
+      <c r="G102" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="52">
         <v>5</v>
       </c>
-      <c r="C103" s="57" t="s">
+      <c r="C103" s="56" t="s">
         <v>445</v>
       </c>
-      <c r="D103" s="53">
+      <c r="D103" s="52">
         <v>5</v>
       </c>
-      <c r="E103" s="53">
+      <c r="E103" s="52">
         <v>5</v>
       </c>
-      <c r="F103" s="53">
+      <c r="F103" s="52">
         <v>5</v>
       </c>
-    </row>
-    <row r="104" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="53">
+      <c r="G103" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="52">
         <v>6</v>
       </c>
-      <c r="C104" s="57" t="s">
+      <c r="C104" s="56" t="s">
         <v>439</v>
       </c>
-      <c r="D104" s="53">
+      <c r="D104" s="52">
         <v>6</v>
       </c>
-      <c r="E104" s="53">
+      <c r="E104" s="52">
         <v>6</v>
       </c>
-      <c r="F104" s="53">
+      <c r="F104" s="52">
         <v>6</v>
       </c>
-    </row>
-    <row r="105" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="53">
+      <c r="G104" s="74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="52">
         <v>7</v>
       </c>
-      <c r="C105" s="57" t="s">
+      <c r="C105" s="56" t="s">
         <v>441</v>
       </c>
-      <c r="D105" s="53">
+      <c r="D105" s="52">
         <v>7</v>
       </c>
-      <c r="E105" s="53">
+      <c r="E105" s="52">
         <v>7</v>
       </c>
-      <c r="F105" s="53">
+      <c r="F105" s="52">
         <v>7</v>
       </c>
-    </row>
-    <row r="106" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="53">
+      <c r="G105" s="74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="52">
         <v>8</v>
       </c>
-      <c r="C106" s="57" t="s">
+      <c r="C106" s="56" t="s">
         <v>445</v>
       </c>
-      <c r="D106" s="53">
+      <c r="D106" s="52">
         <v>8</v>
       </c>
-      <c r="E106" s="53">
+      <c r="E106" s="52">
         <v>8</v>
       </c>
-      <c r="F106" s="53">
+      <c r="F106" s="52">
         <v>8</v>
       </c>
-    </row>
-    <row r="107" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="53">
+      <c r="G106" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="52">
         <v>9</v>
       </c>
-      <c r="C107" s="57" t="s">
+      <c r="C107" s="56" t="s">
         <v>445</v>
       </c>
-      <c r="D107" s="53">
+      <c r="D107" s="52">
         <v>9</v>
       </c>
-      <c r="E107" s="53">
+      <c r="E107" s="52">
         <v>9</v>
       </c>
-      <c r="F107" s="53">
+      <c r="F107" s="52">
         <v>9</v>
       </c>
-    </row>
-    <row r="108" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="53">
+      <c r="G107" s="74">
         <v>10</v>
       </c>
-      <c r="C108" s="57" t="s">
+    </row>
+    <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="52">
+        <v>10</v>
+      </c>
+      <c r="C108" s="56" t="s">
         <v>445</v>
       </c>
-      <c r="D108" s="53">
+      <c r="D108" s="52">
         <v>10</v>
       </c>
-      <c r="E108" s="53">
+      <c r="E108" s="52">
         <v>10</v>
       </c>
-      <c r="F108" s="53">
+      <c r="F108" s="52">
         <v>10</v>
       </c>
-    </row>
-    <row r="109" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="53">
+      <c r="G108" s="74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="52">
         <v>11</v>
       </c>
-      <c r="C109" s="57" t="s">
+      <c r="C109" s="56" t="s">
         <v>452</v>
       </c>
-      <c r="D109" s="53">
+      <c r="D109" s="52">
         <v>11</v>
       </c>
-      <c r="E109" s="53">
+      <c r="E109" s="52">
         <v>2</v>
       </c>
-      <c r="F109" s="53">
+      <c r="F109" s="52">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="53">
+      <c r="G109" s="74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="52">
         <v>12</v>
       </c>
-      <c r="C110" s="57" t="s">
+      <c r="C110" s="56" t="s">
         <v>453</v>
       </c>
-      <c r="D110" s="53">
+      <c r="D110" s="52">
         <v>12</v>
       </c>
-      <c r="E110" s="53">
+      <c r="E110" s="52">
         <v>4</v>
       </c>
-      <c r="F110" s="53">
+      <c r="F110" s="52">
         <v>4</v>
       </c>
-    </row>
-    <row r="111" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="53">
+      <c r="G110" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="52">
         <v>13</v>
       </c>
-      <c r="C111" s="57" t="s">
+      <c r="C111" s="56" t="s">
         <v>454</v>
       </c>
-      <c r="D111" s="53">
+      <c r="D111" s="52">
         <v>13</v>
       </c>
-      <c r="E111" s="53">
+      <c r="E111" s="52">
         <v>6</v>
       </c>
-      <c r="F111" s="53">
+      <c r="F111" s="52">
         <v>6</v>
       </c>
-    </row>
-    <row r="112" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G111" s="74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="49" t="s">
+        <v>535</v>
+      </c>
       <c r="B114" s="48" t="s">
         <v>300</v>
       </c>
-      <c r="E114" s="50" t="s">
+      <c r="E114" s="49" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="115" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="11" t="s">
         <v>301</v>
       </c>
@@ -10332,37 +10426,40 @@
         <v>305</v>
       </c>
     </row>
-    <row r="116" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="67" t="s">
-        <v>459</v>
-      </c>
-      <c r="C116" s="68"/>
-      <c r="D116" s="68"/>
-      <c r="E116" s="68"/>
-      <c r="F116" s="68"/>
-    </row>
-    <row r="117" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="69"/>
-      <c r="C117" s="69"/>
-      <c r="D117" s="69"/>
-      <c r="E117" s="69"/>
-      <c r="F117" s="69"/>
-    </row>
-    <row r="118" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="69"/>
-      <c r="C118" s="69"/>
-      <c r="D118" s="69"/>
-      <c r="E118" s="69"/>
-      <c r="F118" s="69"/>
-    </row>
-    <row r="119" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="69" t="s">
+        <v>550</v>
+      </c>
+      <c r="C116" s="70"/>
+      <c r="D116" s="70"/>
+      <c r="E116" s="70"/>
+      <c r="F116" s="70"/>
+    </row>
+    <row r="117" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="71"/>
+      <c r="C117" s="71"/>
+      <c r="D117" s="71"/>
+      <c r="E117" s="71"/>
+      <c r="F117" s="71"/>
+    </row>
+    <row r="118" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="71"/>
+      <c r="C118" s="71"/>
+      <c r="D118" s="71"/>
+      <c r="E118" s="71"/>
+      <c r="F118" s="71"/>
+    </row>
+    <row r="119" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="49" t="s">
+        <v>534</v>
+      </c>
       <c r="B121" s="48" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="122" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="11" t="s">
         <v>279</v>
       </c>
@@ -10370,46 +10467,49 @@
         <v>280</v>
       </c>
     </row>
-    <row r="123" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="53">
+    <row r="123" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="52">
         <v>1</v>
       </c>
-      <c r="C123" s="53" t="s">
+      <c r="C123" s="52" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="124" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="53">
+    <row r="124" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="52">
         <v>2</v>
       </c>
-      <c r="C124" s="53" t="s">
+      <c r="C124" s="52" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="52">
+        <v>3</v>
+      </c>
+      <c r="C125" s="52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="52">
+        <v>4</v>
+      </c>
+      <c r="C126" s="52" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="125" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="53">
-        <v>3</v>
-      </c>
-      <c r="C125" s="53" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="126" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="53">
-        <v>4</v>
-      </c>
-      <c r="C126" s="53" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="127" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="49" t="s">
+        <v>534</v>
+      </c>
       <c r="B129" s="48" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="130" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="41" t="s">
         <v>283</v>
       </c>
@@ -10420,384 +10520,387 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="64" t="s">
-        <v>462</v>
-      </c>
-      <c r="C131" s="65"/>
-      <c r="D131" s="66"/>
-    </row>
-    <row r="132" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="53">
+    <row r="131" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="66" t="s">
+        <v>461</v>
+      </c>
+      <c r="C131" s="67"/>
+      <c r="D131" s="68"/>
+    </row>
+    <row r="132" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="52">
         <v>1</v>
       </c>
-      <c r="C132" s="53">
+      <c r="C132" s="52">
         <v>1</v>
       </c>
-      <c r="D132" s="53">
+      <c r="D132" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="53">
+    <row r="133" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="52">
         <v>1</v>
       </c>
-      <c r="C133" s="53">
+      <c r="C133" s="52">
         <v>3</v>
       </c>
-      <c r="D133" s="53">
+      <c r="D133" s="52">
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="53">
+    <row r="134" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="52">
         <v>2</v>
       </c>
-      <c r="C134" s="53">
+      <c r="C134" s="52">
         <v>4</v>
       </c>
-      <c r="D134" s="53">
+      <c r="D134" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="53">
+    <row r="135" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="52">
         <v>2</v>
       </c>
-      <c r="C135" s="53">
+      <c r="C135" s="52">
         <v>5</v>
       </c>
-      <c r="D135" s="53">
+      <c r="D135" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="53">
+    <row r="136" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="52">
         <v>3</v>
       </c>
-      <c r="C136" s="53">
+      <c r="C136" s="52">
         <v>6</v>
       </c>
-      <c r="D136" s="53">
+      <c r="D136" s="52">
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="53">
+    <row r="137" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="52">
         <v>3</v>
       </c>
-      <c r="C137" s="53">
+      <c r="C137" s="52">
         <v>2</v>
       </c>
-      <c r="D137" s="53">
+      <c r="D137" s="52">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="53">
+    <row r="138" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="52">
         <v>4</v>
       </c>
-      <c r="C138" s="53">
+      <c r="C138" s="52">
         <v>8</v>
       </c>
-      <c r="D138" s="53">
+      <c r="D138" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="53">
+    <row r="139" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="52">
         <v>4</v>
       </c>
-      <c r="C139" s="53">
+      <c r="C139" s="52">
         <v>12</v>
       </c>
-      <c r="D139" s="53">
+      <c r="D139" s="52">
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="53">
+    <row r="140" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="52">
         <v>5</v>
       </c>
-      <c r="C140" s="53">
+      <c r="C140" s="52">
         <v>88</v>
       </c>
-      <c r="D140" s="53">
+      <c r="D140" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="53">
+    <row r="141" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="52">
         <v>5</v>
       </c>
-      <c r="C141" s="53">
+      <c r="C141" s="52">
         <v>22</v>
       </c>
-      <c r="D141" s="53">
+      <c r="D141" s="52">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="53">
+    <row r="142" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="52">
         <v>5</v>
       </c>
-      <c r="C142" s="53">
+      <c r="C142" s="52">
         <v>11</v>
       </c>
-      <c r="D142" s="53">
+      <c r="D142" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="53">
+    <row r="143" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="52">
         <v>5</v>
       </c>
-      <c r="C143" s="53">
+      <c r="C143" s="52">
         <v>33</v>
       </c>
-      <c r="D143" s="53">
+      <c r="D143" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="53">
+    <row r="144" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="52">
         <v>6</v>
       </c>
-      <c r="C144" s="53">
+      <c r="C144" s="52">
         <v>2</v>
       </c>
-      <c r="D144" s="53">
+      <c r="D144" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="53">
+      <c r="B145" s="52">
         <v>7</v>
       </c>
-      <c r="C145" s="53">
+      <c r="C145" s="52">
         <v>1</v>
       </c>
-      <c r="D145" s="53">
+      <c r="D145" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="146" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="53">
+      <c r="B146" s="52">
         <v>8</v>
       </c>
-      <c r="C146" s="53">
+      <c r="C146" s="52">
         <v>27</v>
       </c>
-      <c r="D146" s="53">
+      <c r="D146" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="53">
+      <c r="B147" s="52">
         <v>8</v>
       </c>
-      <c r="C147" s="53">
+      <c r="C147" s="52">
         <v>23</v>
       </c>
-      <c r="D147" s="53">
+      <c r="D147" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="53">
+      <c r="B148" s="52">
         <v>8</v>
       </c>
-      <c r="C148" s="53">
+      <c r="C148" s="52">
         <v>98</v>
       </c>
-      <c r="D148" s="53">
+      <c r="D148" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="149" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="53">
+      <c r="B149" s="52">
         <v>9</v>
       </c>
-      <c r="C149" s="53">
+      <c r="C149" s="52">
         <v>100</v>
       </c>
-      <c r="D149" s="53">
+      <c r="D149" s="52">
         <v>6</v>
       </c>
     </row>
     <row r="150" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="53">
+      <c r="B150" s="52">
         <v>9</v>
       </c>
-      <c r="C150" s="53">
+      <c r="C150" s="52">
         <v>11</v>
       </c>
-      <c r="D150" s="53">
+      <c r="D150" s="52">
         <v>7</v>
       </c>
     </row>
     <row r="151" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="53">
+      <c r="B151" s="52">
         <v>9</v>
       </c>
-      <c r="C151" s="53">
+      <c r="C151" s="52">
         <v>45</v>
       </c>
-      <c r="D151" s="53">
+      <c r="D151" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="152" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="53">
+      <c r="B152" s="52">
         <v>9</v>
       </c>
-      <c r="C152" s="53">
+      <c r="C152" s="52">
         <v>22</v>
       </c>
-      <c r="D152" s="53">
+      <c r="D152" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="153" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="53">
+      <c r="B153" s="52">
         <v>9</v>
       </c>
-      <c r="C153" s="53">
+      <c r="C153" s="52">
         <v>32</v>
       </c>
-      <c r="D153" s="53">
+      <c r="D153" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="53">
+      <c r="B154" s="52">
         <v>10</v>
       </c>
-      <c r="C154" s="53">
+      <c r="C154" s="52">
         <v>18</v>
       </c>
-      <c r="D154" s="53">
+      <c r="D154" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="155" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="53">
+      <c r="B155" s="52">
         <v>10</v>
       </c>
-      <c r="C155" s="53">
+      <c r="C155" s="52">
         <v>29</v>
       </c>
-      <c r="D155" s="53">
+      <c r="D155" s="52">
         <v>4</v>
       </c>
     </row>
     <row r="156" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="53">
+      <c r="B156" s="52">
         <v>11</v>
       </c>
-      <c r="C156" s="53">
+      <c r="C156" s="52">
         <v>33</v>
       </c>
-      <c r="D156" s="53">
+      <c r="D156" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="157" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="53">
+      <c r="B157" s="52">
         <v>11</v>
       </c>
-      <c r="C157" s="53">
+      <c r="C157" s="52">
         <v>65</v>
       </c>
-      <c r="D157" s="53">
+      <c r="D157" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="53">
+      <c r="B158" s="52">
         <v>11</v>
       </c>
-      <c r="C158" s="53">
+      <c r="C158" s="52">
         <v>1</v>
       </c>
-      <c r="D158" s="53">
+      <c r="D158" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="53">
+      <c r="B159" s="52">
         <v>11</v>
       </c>
-      <c r="C159" s="53">
+      <c r="C159" s="52">
         <v>2</v>
       </c>
-      <c r="D159" s="53">
+      <c r="D159" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="160" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="53">
+      <c r="B160" s="52">
         <v>11</v>
       </c>
-      <c r="C160" s="53">
+      <c r="C160" s="52">
         <v>5</v>
       </c>
-      <c r="D160" s="53">
+      <c r="D160" s="52">
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="53">
+    <row r="161" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="52">
         <v>11</v>
       </c>
-      <c r="C161" s="53">
+      <c r="C161" s="52">
         <v>7</v>
       </c>
-      <c r="D161" s="53">
+      <c r="D161" s="52">
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="53">
+    <row r="162" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="52">
         <v>12</v>
       </c>
-      <c r="C162" s="53">
+      <c r="C162" s="52">
         <v>55</v>
       </c>
-      <c r="D162" s="53">
+      <c r="D162" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="53">
+    <row r="163" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="52">
         <v>13</v>
       </c>
-      <c r="C163" s="53">
+      <c r="C163" s="52">
         <v>92</v>
       </c>
-      <c r="D163" s="53">
+      <c r="D163" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="53">
+    <row r="164" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="52">
         <v>13</v>
       </c>
-      <c r="C164" s="53">
+      <c r="C164" s="52">
         <v>14</v>
       </c>
-      <c r="D164" s="53">
+      <c r="D164" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="49" t="s">
+        <v>534</v>
+      </c>
       <c r="B167" s="48" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="168" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B168" s="11" t="s">
         <v>288</v>
       </c>
@@ -10805,70 +10908,73 @@
         <v>289</v>
       </c>
     </row>
-    <row r="169" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="53">
+    <row r="169" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="52">
         <v>1</v>
       </c>
-      <c r="C169" s="53" t="s">
+      <c r="C169" s="52" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="52">
+        <v>2</v>
+      </c>
+      <c r="C170" s="52" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="170" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="53">
-        <v>2</v>
-      </c>
-      <c r="C170" s="53" t="s">
+    <row r="171" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="52">
+        <v>3</v>
+      </c>
+      <c r="C171" s="52" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="171" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="53">
-        <v>3</v>
-      </c>
-      <c r="C171" s="53" t="s">
+    <row r="172" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="52">
+        <v>4</v>
+      </c>
+      <c r="C172" s="52" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="172" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="53">
-        <v>4</v>
-      </c>
-      <c r="C172" s="53" t="s">
+    <row r="173" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B173" s="52">
+        <v>5</v>
+      </c>
+      <c r="C173" s="52" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="173" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="53">
-        <v>5</v>
-      </c>
-      <c r="C173" s="53" t="s">
+    <row r="174" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="52">
+        <v>6</v>
+      </c>
+      <c r="C174" s="52" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="174" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="53">
-        <v>6</v>
-      </c>
-      <c r="C174" s="53" t="s">
+    <row r="175" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="52">
+        <v>7</v>
+      </c>
+      <c r="C175" s="52" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="175" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="53">
-        <v>7</v>
-      </c>
-      <c r="C175" s="53" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="49" t="s">
+        <v>535</v>
+      </c>
       <c r="B178" s="48" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" s="41" t="s">
         <v>293</v>
       </c>
@@ -10882,73 +10988,76 @@
         <v>296</v>
       </c>
     </row>
-    <row r="180" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="58" t="s">
+    <row r="180" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B180" s="57" t="s">
+        <v>469</v>
+      </c>
+      <c r="C180" s="49"/>
+      <c r="D180" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="C180" s="50"/>
-      <c r="D180" s="50" t="s">
+      <c r="E180" s="44" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B181" s="57" t="s">
         <v>471</v>
       </c>
-      <c r="E180" s="50" t="s">
+      <c r="C181" s="49"/>
+      <c r="D181" s="49" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="181" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="58" t="s">
+      <c r="E181" s="58" t="s">
         <v>473</v>
       </c>
-      <c r="C181" s="50"/>
-      <c r="D181" s="50" t="s">
+    </row>
+    <row r="182" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="57" t="s">
         <v>474</v>
       </c>
-      <c r="E181" s="59" t="s">
+      <c r="C182" s="49"/>
+      <c r="D182" s="49" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="182" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="58" t="s">
+      <c r="E182" s="58" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="57" t="s">
         <v>476</v>
       </c>
-      <c r="C182" s="50"/>
-      <c r="D182" s="50" t="s">
+      <c r="C183" s="49"/>
+      <c r="D183" s="49" t="s">
         <v>477</v>
       </c>
-      <c r="E182" s="59" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="183" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="58" t="s">
+      <c r="E183" s="58" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B184" s="57" t="s">
+        <v>551</v>
+      </c>
+      <c r="C184" s="49"/>
+      <c r="D184" s="49" t="s">
         <v>478</v>
       </c>
-      <c r="C183" s="50"/>
-      <c r="D183" s="50" t="s">
-        <v>479</v>
-      </c>
-      <c r="E183" s="59" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="184" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="58" t="s">
-        <v>480</v>
-      </c>
-      <c r="C184" s="50"/>
-      <c r="D184" s="50" t="s">
-        <v>481</v>
-      </c>
-      <c r="E184" s="50"/>
-    </row>
-    <row r="185" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E184" s="49"/>
+    </row>
+    <row r="185" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="49" t="s">
+        <v>534</v>
+      </c>
       <c r="B188" s="48" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" s="11" t="s">
         <v>307</v>
       </c>
@@ -10970,31 +11079,31 @@
       <c r="H189" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="J189" s="73" t="s">
+      <c r="J189" s="62" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="190" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="53">
+    <row r="190" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B190" s="52">
         <v>1</v>
       </c>
-      <c r="C190" s="53" t="s">
+      <c r="C190" s="52" t="s">
+        <v>479</v>
+      </c>
+      <c r="D190" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="E190" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="F190" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G190" s="59" t="s">
         <v>482</v>
       </c>
-      <c r="D190" s="57" t="s">
-        <v>483</v>
-      </c>
-      <c r="E190" s="53" t="s">
-        <v>438</v>
-      </c>
-      <c r="F190" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G190" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H190" s="53" t="s">
-        <v>484</v>
+      <c r="H190" s="52" t="s">
+        <v>481</v>
       </c>
       <c r="J190" s="11" t="s">
         <v>323</v>
@@ -11003,249 +11112,249 @@
         <v>324</v>
       </c>
     </row>
-    <row r="191" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="53">
+    <row r="191" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B191" s="52">
         <v>2</v>
       </c>
-      <c r="C191" s="53" t="s">
+      <c r="C191" s="52" t="s">
+        <v>483</v>
+      </c>
+      <c r="D191" s="52" t="s">
+        <v>484</v>
+      </c>
+      <c r="E191" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="F191" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G191" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H191" s="52" t="s">
+        <v>485</v>
+      </c>
+      <c r="J191" s="52">
+        <v>1</v>
+      </c>
+      <c r="K191" s="52" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B192" s="52">
+        <v>3</v>
+      </c>
+      <c r="C192" s="52" t="s">
         <v>486</v>
       </c>
-      <c r="D191" s="53" t="s">
+      <c r="D192" s="52" t="s">
         <v>487</v>
       </c>
-      <c r="E191" s="53" t="s">
-        <v>440</v>
-      </c>
-      <c r="F191" s="53">
+      <c r="E192" s="52" t="s">
+        <v>442</v>
+      </c>
+      <c r="F192" s="52">
         <v>123456789</v>
       </c>
-      <c r="G191" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H191" s="53" t="s">
+      <c r="G192" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H192" s="52" t="s">
         <v>488</v>
       </c>
-      <c r="J191" s="53">
-        <v>1</v>
-      </c>
-      <c r="K191" s="53" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="192" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="53">
+      <c r="J192" s="52">
+        <v>2</v>
+      </c>
+      <c r="K192" s="52" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="193" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="52">
+        <v>4</v>
+      </c>
+      <c r="C193" s="52" t="s">
+        <v>489</v>
+      </c>
+      <c r="D193" s="52" t="s">
+        <v>490</v>
+      </c>
+      <c r="E193" s="52" t="s">
+        <v>444</v>
+      </c>
+      <c r="F193" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G193" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H193" s="52" t="s">
+        <v>491</v>
+      </c>
+      <c r="J193" s="52">
         <v>3</v>
       </c>
-      <c r="C192" s="53" t="s">
-        <v>489</v>
-      </c>
-      <c r="D192" s="53" t="s">
-        <v>490</v>
-      </c>
-      <c r="E192" s="53" t="s">
-        <v>442</v>
-      </c>
-      <c r="F192" s="53">
+      <c r="K193" s="52" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="194" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B194" s="52">
+        <v>5</v>
+      </c>
+      <c r="C194" s="52" t="s">
+        <v>492</v>
+      </c>
+      <c r="D194" s="52" t="s">
+        <v>493</v>
+      </c>
+      <c r="E194" s="52" t="s">
+        <v>446</v>
+      </c>
+      <c r="F194" s="52">
         <v>123456789</v>
       </c>
-      <c r="G192" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H192" s="53" t="s">
-        <v>491</v>
-      </c>
-      <c r="J192" s="53">
-        <v>2</v>
-      </c>
-      <c r="K192" s="53" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="193" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="53">
+      <c r="G194" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H194" s="52" t="s">
+        <v>494</v>
+      </c>
+      <c r="J194" s="52">
         <v>4</v>
       </c>
-      <c r="C193" s="53" t="s">
-        <v>492</v>
-      </c>
-      <c r="D193" s="53" t="s">
-        <v>493</v>
-      </c>
-      <c r="E193" s="53" t="s">
-        <v>444</v>
-      </c>
-      <c r="F193" s="53">
+      <c r="K194" s="52" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="195" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B195" s="52">
+        <v>6</v>
+      </c>
+      <c r="C195" s="52" t="s">
+        <v>495</v>
+      </c>
+      <c r="D195" s="52" t="s">
+        <v>496</v>
+      </c>
+      <c r="E195" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="F195" s="52">
         <v>123456789</v>
       </c>
-      <c r="G193" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H193" s="53" t="s">
-        <v>494</v>
-      </c>
-      <c r="J193" s="53">
-        <v>3</v>
-      </c>
-      <c r="K193" s="53" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="194" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="53">
-        <v>5</v>
-      </c>
-      <c r="C194" s="53" t="s">
-        <v>495</v>
-      </c>
-      <c r="D194" s="53" t="s">
-        <v>496</v>
-      </c>
-      <c r="E194" s="53" t="s">
-        <v>446</v>
-      </c>
-      <c r="F194" s="53">
+      <c r="G195" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H195" s="52" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B196" s="52">
+        <v>7</v>
+      </c>
+      <c r="C196" s="52" t="s">
+        <v>498</v>
+      </c>
+      <c r="D196" s="52" t="s">
+        <v>499</v>
+      </c>
+      <c r="E196" s="52" t="s">
+        <v>448</v>
+      </c>
+      <c r="F196" s="52">
         <v>123456789</v>
       </c>
-      <c r="G194" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H194" s="53" t="s">
-        <v>497</v>
-      </c>
-      <c r="J194" s="53">
-        <v>4</v>
-      </c>
-      <c r="K194" s="53" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="195" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="53">
-        <v>6</v>
-      </c>
-      <c r="C195" s="53" t="s">
-        <v>498</v>
-      </c>
-      <c r="D195" s="53" t="s">
-        <v>499</v>
-      </c>
-      <c r="E195" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="F195" s="53">
+      <c r="G196" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H196" s="52" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B197" s="52">
+        <v>8</v>
+      </c>
+      <c r="C197" s="52" t="s">
+        <v>501</v>
+      </c>
+      <c r="D197" s="52" t="s">
+        <v>502</v>
+      </c>
+      <c r="E197" s="52" t="s">
+        <v>449</v>
+      </c>
+      <c r="F197" s="52">
         <v>123456789</v>
       </c>
-      <c r="G195" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H195" s="53" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="196" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="53">
-        <v>7</v>
-      </c>
-      <c r="C196" s="53" t="s">
-        <v>501</v>
-      </c>
-      <c r="D196" s="53" t="s">
-        <v>502</v>
-      </c>
-      <c r="E196" s="53" t="s">
-        <v>448</v>
-      </c>
-      <c r="F196" s="53">
+      <c r="G197" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H197" s="52" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="198" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B198" s="52">
+        <v>9</v>
+      </c>
+      <c r="C198" s="52" t="s">
+        <v>504</v>
+      </c>
+      <c r="D198" s="52" t="s">
+        <v>505</v>
+      </c>
+      <c r="E198" s="52" t="s">
+        <v>450</v>
+      </c>
+      <c r="F198" s="52">
         <v>123456789</v>
       </c>
-      <c r="G196" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H196" s="53" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="197" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B197" s="53">
-        <v>8</v>
-      </c>
-      <c r="C197" s="53" t="s">
-        <v>504</v>
-      </c>
-      <c r="D197" s="53" t="s">
-        <v>505</v>
-      </c>
-      <c r="E197" s="53" t="s">
-        <v>449</v>
-      </c>
-      <c r="F197" s="53">
+      <c r="G198" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H198" s="52" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="52">
+        <v>10</v>
+      </c>
+      <c r="C199" s="52" t="s">
+        <v>507</v>
+      </c>
+      <c r="D199" s="52" t="s">
+        <v>508</v>
+      </c>
+      <c r="E199" s="52" t="s">
+        <v>451</v>
+      </c>
+      <c r="F199" s="52">
         <v>123456789</v>
       </c>
-      <c r="G197" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H197" s="53" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="198" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B198" s="53">
-        <v>9</v>
-      </c>
-      <c r="C198" s="53" t="s">
-        <v>507</v>
-      </c>
-      <c r="D198" s="53" t="s">
-        <v>508</v>
-      </c>
-      <c r="E198" s="53" t="s">
-        <v>450</v>
-      </c>
-      <c r="F198" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G198" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H198" s="53" t="s">
+      <c r="G199" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H199" s="52" t="s">
         <v>509</v>
-      </c>
-    </row>
-    <row r="199" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="53">
-        <v>10</v>
-      </c>
-      <c r="C199" s="53" t="s">
-        <v>510</v>
-      </c>
-      <c r="D199" s="53" t="s">
-        <v>511</v>
-      </c>
-      <c r="E199" s="53" t="s">
-        <v>451</v>
-      </c>
-      <c r="F199" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G199" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H199" s="53" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="200" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="201" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I201" s="50" t="s">
-        <v>550</v>
+      <c r="I201" s="49" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="202" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="48" t="s">
+      <c r="B202" s="62" t="s">
         <v>314</v>
       </c>
-      <c r="I202" s="72" t="s">
-        <v>548</v>
+      <c r="I202" s="61" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="203" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11275,273 +11384,273 @@
       </c>
     </row>
     <row r="204" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B204" s="53">
+      <c r="B204" s="52">
         <v>1</v>
       </c>
-      <c r="C204" s="53" t="s">
-        <v>471</v>
-      </c>
-      <c r="D204" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="E204" s="53" t="s">
+      <c r="C204" s="52" t="s">
+        <v>470</v>
+      </c>
+      <c r="D204" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="E204" s="52" t="s">
         <v>438</v>
       </c>
-      <c r="F204" s="53">
+      <c r="F204" s="52">
         <v>123456789</v>
       </c>
-      <c r="G204" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H204" s="53" t="s">
+      <c r="G204" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H204" s="52" t="s">
+        <v>519</v>
+      </c>
+      <c r="I204" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B205" s="52">
+        <v>2</v>
+      </c>
+      <c r="C205" s="52" t="s">
+        <v>518</v>
+      </c>
+      <c r="D205" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="E205" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="F205" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G205" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H205" s="52" t="s">
+        <v>520</v>
+      </c>
+      <c r="I205" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="52">
+        <v>3</v>
+      </c>
+      <c r="C206" s="52" t="s">
+        <v>517</v>
+      </c>
+      <c r="D206" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="E206" s="52" t="s">
+        <v>442</v>
+      </c>
+      <c r="F206" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G206" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H206" s="52" t="s">
+        <v>521</v>
+      </c>
+      <c r="I206" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B207" s="52">
+        <v>4</v>
+      </c>
+      <c r="C207" s="52" t="s">
+        <v>516</v>
+      </c>
+      <c r="D207" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="E207" s="52" t="s">
+        <v>444</v>
+      </c>
+      <c r="F207" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G207" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H207" s="52" t="s">
         <v>522</v>
       </c>
-      <c r="I204" s="53">
+      <c r="I207" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="53">
+    <row r="208" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B208" s="52">
+        <v>5</v>
+      </c>
+      <c r="C208" s="52" t="s">
+        <v>515</v>
+      </c>
+      <c r="D208" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="E208" s="52" t="s">
+        <v>446</v>
+      </c>
+      <c r="F208" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G208" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H208" s="52" t="s">
+        <v>523</v>
+      </c>
+      <c r="I208" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B209" s="52">
+        <v>6</v>
+      </c>
+      <c r="C209" s="52" t="s">
+        <v>514</v>
+      </c>
+      <c r="D209" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="E209" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="F209" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G209" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H209" s="52" t="s">
+        <v>524</v>
+      </c>
+      <c r="I209" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B210" s="52">
+        <v>7</v>
+      </c>
+      <c r="C210" s="52" t="s">
+        <v>513</v>
+      </c>
+      <c r="D210" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="E210" s="52" t="s">
+        <v>448</v>
+      </c>
+      <c r="F210" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G210" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H210" s="52" t="s">
+        <v>525</v>
+      </c>
+      <c r="I210" s="52">
         <v>2</v>
       </c>
-      <c r="C205" s="53" t="s">
-        <v>521</v>
-      </c>
-      <c r="D205" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="E205" s="53" t="s">
-        <v>440</v>
-      </c>
-      <c r="F205" s="53">
+    </row>
+    <row r="211" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B211" s="52">
+        <v>8</v>
+      </c>
+      <c r="C211" s="52" t="s">
+        <v>512</v>
+      </c>
+      <c r="D211" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="E211" s="52" t="s">
+        <v>449</v>
+      </c>
+      <c r="F211" s="52">
         <v>123456789</v>
       </c>
-      <c r="G205" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H205" s="53" t="s">
-        <v>523</v>
-      </c>
-      <c r="I205" s="53">
+      <c r="G211" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H211" s="52" t="s">
+        <v>526</v>
+      </c>
+      <c r="I211" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B212" s="52">
+        <v>9</v>
+      </c>
+      <c r="C212" s="52" t="s">
+        <v>511</v>
+      </c>
+      <c r="D212" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="E212" s="52" t="s">
+        <v>450</v>
+      </c>
+      <c r="F212" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G212" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H212" s="52" t="s">
+        <v>527</v>
+      </c>
+      <c r="I212" s="52">
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="53">
-        <v>3</v>
-      </c>
-      <c r="C206" s="53" t="s">
-        <v>520</v>
-      </c>
-      <c r="D206" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="E206" s="53" t="s">
-        <v>442</v>
-      </c>
-      <c r="F206" s="53">
+    <row r="213" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B213" s="52">
+        <v>10</v>
+      </c>
+      <c r="C213" s="52" t="s">
+        <v>510</v>
+      </c>
+      <c r="D213" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="E213" s="52" t="s">
+        <v>451</v>
+      </c>
+      <c r="F213" s="52">
         <v>123456789</v>
       </c>
-      <c r="G206" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H206" s="53" t="s">
-        <v>524</v>
-      </c>
-      <c r="I206" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="207" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B207" s="53">
+      <c r="G213" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H213" s="52" t="s">
+        <v>528</v>
+      </c>
+      <c r="I213" s="52">
         <v>4</v>
       </c>
-      <c r="C207" s="53" t="s">
-        <v>519</v>
-      </c>
-      <c r="D207" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="E207" s="53" t="s">
-        <v>444</v>
-      </c>
-      <c r="F207" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G207" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H207" s="53" t="s">
-        <v>525</v>
-      </c>
-      <c r="I207" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B208" s="53">
-        <v>5</v>
-      </c>
-      <c r="C208" s="53" t="s">
-        <v>518</v>
-      </c>
-      <c r="D208" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="E208" s="53" t="s">
-        <v>446</v>
-      </c>
-      <c r="F208" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G208" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H208" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="I208" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B209" s="53">
-        <v>6</v>
-      </c>
-      <c r="C209" s="53" t="s">
-        <v>517</v>
-      </c>
-      <c r="D209" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="E209" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="F209" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G209" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H209" s="53" t="s">
-        <v>527</v>
-      </c>
-      <c r="I209" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B210" s="53">
-        <v>7</v>
-      </c>
-      <c r="C210" s="53" t="s">
-        <v>516</v>
-      </c>
-      <c r="D210" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="E210" s="53" t="s">
-        <v>448</v>
-      </c>
-      <c r="F210" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G210" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H210" s="53" t="s">
-        <v>528</v>
-      </c>
-      <c r="I210" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="211" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B211" s="53">
-        <v>8</v>
-      </c>
-      <c r="C211" s="53" t="s">
-        <v>515</v>
-      </c>
-      <c r="D211" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="E211" s="53" t="s">
-        <v>449</v>
-      </c>
-      <c r="F211" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G211" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H211" s="53" t="s">
-        <v>529</v>
-      </c>
-      <c r="I211" s="53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="212" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B212" s="53">
-        <v>9</v>
-      </c>
-      <c r="C212" s="53" t="s">
-        <v>514</v>
-      </c>
-      <c r="D212" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="E212" s="53" t="s">
-        <v>450</v>
-      </c>
-      <c r="F212" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G212" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H212" s="53" t="s">
-        <v>530</v>
-      </c>
-      <c r="I212" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B213" s="53">
-        <v>10</v>
-      </c>
-      <c r="C213" s="53" t="s">
-        <v>513</v>
-      </c>
-      <c r="D213" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="E213" s="53" t="s">
-        <v>451</v>
-      </c>
-      <c r="F213" s="53">
-        <v>123456789</v>
-      </c>
-      <c r="G213" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="H213" s="53" t="s">
-        <v>531</v>
-      </c>
-      <c r="I213" s="53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B216" s="48" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="217" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B217" s="11" t="s">
         <v>327</v>
       </c>
@@ -11552,43 +11661,46 @@
         <v>329</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>330</v>
+        <v>553</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="218" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="67" t="s">
-        <v>532</v>
-      </c>
-      <c r="C218" s="68"/>
-      <c r="D218" s="68"/>
-      <c r="E218" s="68"/>
-      <c r="F218" s="68"/>
-    </row>
-    <row r="219" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="69"/>
-      <c r="C219" s="69"/>
-      <c r="D219" s="69"/>
-      <c r="E219" s="69"/>
-      <c r="F219" s="69"/>
-    </row>
-    <row r="220" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="69"/>
-      <c r="C220" s="69"/>
-      <c r="D220" s="69"/>
-      <c r="E220" s="69"/>
-      <c r="F220" s="69"/>
-    </row>
-    <row r="221" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="75" t="s">
+        <v>554</v>
+      </c>
+      <c r="C218" s="76"/>
+      <c r="D218" s="76"/>
+      <c r="E218" s="76"/>
+      <c r="F218" s="76"/>
+    </row>
+    <row r="219" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="77"/>
+      <c r="C219" s="77"/>
+      <c r="D219" s="77"/>
+      <c r="E219" s="77"/>
+      <c r="F219" s="77"/>
+    </row>
+    <row r="220" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="77"/>
+      <c r="C220" s="77"/>
+      <c r="D220" s="77"/>
+      <c r="E220" s="77"/>
+      <c r="F220" s="77"/>
+    </row>
+    <row r="221" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="49" t="s">
+        <v>534</v>
+      </c>
       <c r="B223" s="48" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B224" s="11" t="s">
         <v>333</v>
       </c>
@@ -11608,52 +11720,179 @@
         <v>338</v>
       </c>
     </row>
-    <row r="225" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B232" s="61" t="s">
+    <row r="225" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" s="80" t="s">
+        <v>555</v>
+      </c>
+      <c r="C225" s="79"/>
+      <c r="D225" s="79"/>
+      <c r="E225" s="79"/>
+      <c r="F225" s="79"/>
+      <c r="G225" s="79"/>
+    </row>
+    <row r="226" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B226" s="78"/>
+      <c r="C226" s="78"/>
+      <c r="D226" s="78"/>
+      <c r="E226" s="78"/>
+      <c r="F226" s="78"/>
+      <c r="G226" s="78"/>
+    </row>
+    <row r="227" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="49" t="s">
+        <v>534</v>
+      </c>
+      <c r="B229" s="60" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="233" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B233" s="11" t="s">
+    <row r="230" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C233" s="38" t="s">
+      <c r="C230" s="38" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="234" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B231" s="52">
+        <v>1</v>
+      </c>
+      <c r="C231" s="52" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" s="52">
+        <v>2</v>
+      </c>
+      <c r="C232" s="52" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B233" s="52">
+        <v>3</v>
+      </c>
+      <c r="C233" s="52" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B234" s="52">
+        <v>4</v>
+      </c>
+      <c r="C234" s="52" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B235" s="52">
+        <v>5</v>
+      </c>
+      <c r="C235" s="52" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="49" t="s">
+        <v>534</v>
+      </c>
+      <c r="B237" s="48" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B238" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="C238" s="41" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B239" s="52">
+        <v>1</v>
+      </c>
+      <c r="C239" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" s="52">
+        <v>2</v>
+      </c>
+      <c r="C240" s="52">
+        <v>2</v>
+      </c>
+    </row>
     <row r="241" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B241" s="48" t="s">
-        <v>342</v>
+      <c r="B241" s="52">
+        <v>3</v>
+      </c>
+      <c r="C241" s="52">
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B242" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="C242" s="41" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="243" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B242" s="52">
+        <v>4</v>
+      </c>
+      <c r="C242" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B243" s="52">
+        <v>5</v>
+      </c>
+      <c r="C243" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B244" s="52">
+        <v>6</v>
+      </c>
+      <c r="C244" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B245" s="52">
+        <v>7</v>
+      </c>
+      <c r="C245" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B246" s="52">
+        <v>8</v>
+      </c>
+      <c r="C246" s="52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B247" s="52">
+        <v>9</v>
+      </c>
+      <c r="C247" s="52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B248" s="52">
+        <v>10</v>
+      </c>
+      <c r="C248" s="52">
+        <v>5</v>
+      </c>
+    </row>
     <row r="249" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="250" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="251" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12407,7 +12646,8 @@
     <row r="999" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B225:G226"/>
     <mergeCell ref="B131:D131"/>
     <mergeCell ref="B218:F220"/>
     <mergeCell ref="C43:F46"/>

--- a/1. Database Design/Java24 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java24 QuyenPhan Database Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3DC602-657D-4999-9A90-0C60DE39EE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D6F90C-AF3E-4FED-A40B-FF5280567487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="433" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1502,7 +1502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D189" authorId="2" shapeId="0" xr:uid="{9BDC8936-92C9-43A1-9379-AB9B7024CE45}">
+    <comment ref="D188" authorId="2" shapeId="0" xr:uid="{9BDC8936-92C9-43A1-9379-AB9B7024CE45}">
       <text>
         <r>
           <rPr>
@@ -1526,7 +1526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G189" authorId="2" shapeId="0" xr:uid="{6AE8310D-3BF7-4201-92B2-A2B94D757B52}">
+    <comment ref="G188" authorId="2" shapeId="0" xr:uid="{6AE8310D-3BF7-4201-92B2-A2B94D757B52}">
       <text>
         <r>
           <rPr>
@@ -1550,7 +1550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D203" authorId="2" shapeId="0" xr:uid="{9B933F05-4824-40FF-A0CC-44296B8D3399}">
+    <comment ref="D202" authorId="2" shapeId="0" xr:uid="{9B933F05-4824-40FF-A0CC-44296B8D3399}">
       <text>
         <r>
           <rPr>
@@ -1574,7 +1574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G203" authorId="2" shapeId="0" xr:uid="{A1ACCF64-494E-4A04-BC4E-BB52726C36B4}">
+    <comment ref="G202" authorId="2" shapeId="0" xr:uid="{A1ACCF64-494E-4A04-BC4E-BB52726C36B4}">
       <text>
         <r>
           <rPr>
@@ -1598,7 +1598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C224" authorId="2" shapeId="0" xr:uid="{650603E4-1922-4F3D-BF57-A44480C7E756}">
+    <comment ref="C223" authorId="2" shapeId="0" xr:uid="{650603E4-1922-4F3D-BF57-A44480C7E756}">
       <text>
         <r>
           <rPr>
@@ -1612,7 +1612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D224" authorId="2" shapeId="0" xr:uid="{23A98BCD-8F58-45E6-803E-7B59DCF7EE56}">
+    <comment ref="D223" authorId="2" shapeId="0" xr:uid="{23A98BCD-8F58-45E6-803E-7B59DCF7EE56}">
       <text>
         <r>
           <rPr>
@@ -1636,7 +1636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E224" authorId="2" shapeId="0" xr:uid="{2B9AFA3A-E429-42C7-BCF0-DD3595633DCF}">
+    <comment ref="E223" authorId="2" shapeId="0" xr:uid="{2B9AFA3A-E429-42C7-BCF0-DD3595633DCF}">
       <text>
         <r>
           <rPr>
@@ -1660,7 +1660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G224" authorId="2" shapeId="0" xr:uid="{90AC3731-A473-470A-BB5D-0A799C6457A9}">
+    <comment ref="G223" authorId="2" shapeId="0" xr:uid="{90AC3731-A473-470A-BB5D-0A799C6457A9}">
       <text>
         <r>
           <rPr>
@@ -3392,9 +3392,6 @@
     <t>T18 10 Địa Chỉ</t>
   </si>
   <si>
-    <t>T16 5 Nhân Viên</t>
-  </si>
-  <si>
     <t>T19</t>
   </si>
   <si>
@@ -3404,9 +3401,6 @@
     <t>Ví điện tử</t>
   </si>
   <si>
-    <t>Quan trọng, cần có dữ liệu chính xác để demo nhiều trường hợp</t>
-  </si>
-  <si>
     <t>Chờ xác nhận</t>
   </si>
   <si>
@@ -3458,9 +3452,6 @@
     <t>Nhân Viên 5</t>
   </si>
   <si>
-    <t>Lê Tèo</t>
-  </si>
-  <si>
     <t>c1@gmal.com</t>
   </si>
   <si>
@@ -3470,79 +3461,52 @@
     <t>$2a$12$w0bs0MW/O3nTyMhuv0r1jOjq2gOaxLxkZgms7u/khHRmtCh3S/Hpu</t>
   </si>
   <si>
-    <t>Văn An</t>
-  </si>
-  <si>
     <t>c2@gmal.com</t>
   </si>
   <si>
     <t>c2auto</t>
   </si>
   <si>
-    <t>Nguyễn A</t>
-  </si>
-  <si>
     <t>c3@gmal.com</t>
   </si>
   <si>
     <t>c3def</t>
   </si>
   <si>
-    <t>Phan Tuấn</t>
-  </si>
-  <si>
     <t>c4@gmal.com</t>
   </si>
   <si>
     <t>c4auto</t>
   </si>
   <si>
-    <t>Hoàng Tiên</t>
-  </si>
-  <si>
     <t>c5@gmal.com</t>
   </si>
   <si>
     <t>c5def</t>
   </si>
   <si>
-    <t>Phạm Ngọc</t>
-  </si>
-  <si>
     <t>c6@gmal.com</t>
   </si>
   <si>
     <t>c6auto</t>
   </si>
   <si>
-    <t>Đoạn Tú</t>
-  </si>
-  <si>
     <t>c7@gmal.com</t>
   </si>
   <si>
     <t>c7def</t>
   </si>
   <si>
-    <t>Hoàng B</t>
-  </si>
-  <si>
     <t>c8@gmal.com</t>
   </si>
   <si>
     <t>c8auto</t>
   </si>
   <si>
-    <t>Lê Huân</t>
-  </si>
-  <si>
     <t>c9@gmal.com</t>
   </si>
   <si>
     <t>c9def</t>
-  </si>
-  <si>
-    <t>Nam Ban</t>
   </si>
   <si>
     <t>c10@gmal.com</t>
@@ -3726,6 +3690,42 @@
   </si>
   <si>
     <t>Role 5</t>
+  </si>
+  <si>
+    <t>Khách hàng 1</t>
+  </si>
+  <si>
+    <t>Khách hàng 2</t>
+  </si>
+  <si>
+    <t>Khách hàng 3</t>
+  </si>
+  <si>
+    <t>Khách hàng 4</t>
+  </si>
+  <si>
+    <t>Khách hàng 5</t>
+  </si>
+  <si>
+    <t>Khách hàng 6</t>
+  </si>
+  <si>
+    <t>Khách hàng 7</t>
+  </si>
+  <si>
+    <t>Khách hàng 8</t>
+  </si>
+  <si>
+    <t>Khách hàng 9</t>
+  </si>
+  <si>
+    <t>Khách hàng 10</t>
+  </si>
+  <si>
+    <t>T16 10 Nhân Viên</t>
+  </si>
+  <si>
+    <t>C12_ITEM_DETAIL_ID</t>
   </si>
 </sst>
 </file>
@@ -4007,7 +4007,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -4063,43 +4063,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -4114,7 +4077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4291,7 +4254,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4309,32 +4272,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4346,13 +4291,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9133,7 +9084,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C125E9-733D-4F85-B782-7EFA49F565B4}">
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:K999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="49" customWidth="1"/>
@@ -9150,14 +9101,14 @@
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B2" s="63" t="s">
         <v>215</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="E2" s="49"/>
     </row>
@@ -9459,7 +9410,7 @@
     <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="B26" s="63" t="s">
         <v>218</v>
@@ -9626,16 +9577,16 @@
     <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="49" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B40" s="62" t="s">
         <v>222</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="E40" s="49"/>
       <c r="F40" s="49"/>
@@ -9673,54 +9624,54 @@
       <c r="C43" s="72" t="s">
         <v>422</v>
       </c>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
       <c r="G43" s="49"/>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="49"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
       <c r="G44" s="49"/>
     </row>
     <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="49"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="71"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
       <c r="G45" s="49"/>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="49"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
       <c r="G46" s="49"/>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="44" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="55" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="49" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B49" s="62" t="s">
         <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -9738,7 +9689,7 @@
       <c r="B51" s="2">
         <v>1</v>
       </c>
-      <c r="C51" s="73" t="s">
+      <c r="C51" s="74" t="s">
         <v>425</v>
       </c>
       <c r="D51" s="2">
@@ -9749,7 +9700,7 @@
       <c r="B52" s="2">
         <v>2</v>
       </c>
-      <c r="C52" s="73"/>
+      <c r="C52" s="74"/>
       <c r="D52" s="2">
         <v>2</v>
       </c>
@@ -9758,7 +9709,7 @@
       <c r="B53" s="2">
         <v>3</v>
       </c>
-      <c r="C53" s="73"/>
+      <c r="C53" s="74"/>
       <c r="D53" s="2">
         <v>3</v>
       </c>
@@ -9767,7 +9718,7 @@
       <c r="B54" s="2">
         <v>4</v>
       </c>
-      <c r="C54" s="73"/>
+      <c r="C54" s="74"/>
       <c r="D54" s="2">
         <v>4</v>
       </c>
@@ -9776,7 +9727,7 @@
       <c r="B55" s="2">
         <v>5</v>
       </c>
-      <c r="C55" s="73"/>
+      <c r="C55" s="74"/>
       <c r="D55" s="2">
         <v>5</v>
       </c>
@@ -9785,7 +9736,7 @@
       <c r="B56" s="2">
         <v>6</v>
       </c>
-      <c r="C56" s="73"/>
+      <c r="C56" s="74"/>
       <c r="D56" s="2">
         <v>6</v>
       </c>
@@ -9794,7 +9745,7 @@
       <c r="B57" s="2">
         <v>7</v>
       </c>
-      <c r="C57" s="73"/>
+      <c r="C57" s="74"/>
       <c r="D57" s="2">
         <v>7</v>
       </c>
@@ -9803,7 +9754,7 @@
       <c r="B58" s="2">
         <v>8</v>
       </c>
-      <c r="C58" s="73"/>
+      <c r="C58" s="74"/>
       <c r="D58" s="2">
         <v>8</v>
       </c>
@@ -9812,7 +9763,7 @@
       <c r="B59" s="2">
         <v>9</v>
       </c>
-      <c r="C59" s="73"/>
+      <c r="C59" s="74"/>
       <c r="D59" s="2">
         <v>9</v>
       </c>
@@ -9821,7 +9772,7 @@
       <c r="B60" s="2">
         <v>10</v>
       </c>
-      <c r="C60" s="73"/>
+      <c r="C60" s="74"/>
       <c r="D60" s="2">
         <v>10</v>
       </c>
@@ -9830,16 +9781,16 @@
     <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="49" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B63" s="62" t="s">
         <v>248</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="F63" s="49" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -9863,35 +9814,35 @@
       <c r="B65" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C65" s="69" t="s">
-        <v>541</v>
-      </c>
-      <c r="D65" s="70"/>
-      <c r="E65" s="70"/>
-      <c r="F65" s="70"/>
+      <c r="C65" s="75" t="s">
+        <v>529</v>
+      </c>
+      <c r="D65" s="76"/>
+      <c r="E65" s="76"/>
+      <c r="F65" s="76"/>
     </row>
     <row r="66" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="71"/>
-      <c r="D66" s="71"/>
-      <c r="E66" s="71"/>
-      <c r="F66" s="71"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="73"/>
+      <c r="E66" s="73"/>
+      <c r="F66" s="73"/>
     </row>
     <row r="67" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
     </row>
     <row r="68" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
     </row>
     <row r="69" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="70" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B70" s="62" t="s">
         <v>254</v>
@@ -9967,7 +9918,7 @@
     <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="49" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B79" s="62" t="s">
         <v>260</v>
@@ -9985,7 +9936,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="2">
         <v>1</v>
       </c>
@@ -9996,7 +9947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
         <v>2</v>
       </c>
@@ -10007,7 +9958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="2">
         <v>3</v>
       </c>
@@ -10018,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
         <v>4</v>
       </c>
@@ -10029,7 +9980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="2">
         <v>5</v>
       </c>
@@ -10040,7 +9991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="2">
         <v>6</v>
       </c>
@@ -10051,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="2">
         <v>7</v>
       </c>
@@ -10062,17 +10013,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="49" t="s">
-        <v>535</v>
-      </c>
-      <c r="B90" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="B90" s="62" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="11" t="s">
         <v>268</v>
       </c>
@@ -10080,40 +10031,41 @@
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="69" t="s">
+    <row r="92" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="75" t="s">
         <v>436</v>
       </c>
-      <c r="C92" s="70"/>
-    </row>
-    <row r="93" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="71"/>
-      <c r="C93" s="71"/>
-    </row>
-    <row r="94" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="71"/>
-      <c r="C94" s="71"/>
-    </row>
-    <row r="95" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C92" s="76"/>
+    </row>
+    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="73"/>
+      <c r="C93" s="73"/>
+    </row>
+    <row r="94" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="73"/>
+      <c r="C94" s="73"/>
+    </row>
+    <row r="95" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D96" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="E96" s="49" t="s">
+        <v>455</v>
+      </c>
+      <c r="F96" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="G96" s="49" t="s">
+        <v>559</v>
+      </c>
+    </row>
     <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B97" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="B97" s="62" t="s">
         <v>275</v>
-      </c>
-      <c r="D97" s="49" t="s">
-        <v>549</v>
-      </c>
-      <c r="E97" s="49" t="s">
-        <v>455</v>
-      </c>
-      <c r="F97" s="49" t="s">
-        <v>456</v>
-      </c>
-      <c r="G97" s="49" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10152,7 +10104,7 @@
       <c r="F99" s="52">
         <v>1</v>
       </c>
-      <c r="G99" s="74">
+      <c r="G99" s="52">
         <v>1</v>
       </c>
     </row>
@@ -10164,7 +10116,7 @@
         <v>439</v>
       </c>
       <c r="D100" s="52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="52">
         <v>2</v>
@@ -10172,7 +10124,7 @@
       <c r="F100" s="52">
         <v>2</v>
       </c>
-      <c r="G100" s="74">
+      <c r="G100" s="52">
         <v>2</v>
       </c>
     </row>
@@ -10184,7 +10136,7 @@
         <v>441</v>
       </c>
       <c r="D101" s="52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" s="52">
         <v>3</v>
@@ -10192,7 +10144,7 @@
       <c r="F101" s="52">
         <v>3</v>
       </c>
-      <c r="G101" s="74">
+      <c r="G101" s="52">
         <v>3</v>
       </c>
     </row>
@@ -10204,7 +10156,7 @@
         <v>443</v>
       </c>
       <c r="D102" s="52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E102" s="52">
         <v>4</v>
@@ -10212,7 +10164,7 @@
       <c r="F102" s="52">
         <v>4</v>
       </c>
-      <c r="G102" s="74">
+      <c r="G102" s="52">
         <v>4</v>
       </c>
     </row>
@@ -10224,7 +10176,7 @@
         <v>445</v>
       </c>
       <c r="D103" s="52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" s="52">
         <v>5</v>
@@ -10232,7 +10184,7 @@
       <c r="F103" s="52">
         <v>5</v>
       </c>
-      <c r="G103" s="74">
+      <c r="G103" s="52">
         <v>5</v>
       </c>
     </row>
@@ -10244,7 +10196,7 @@
         <v>439</v>
       </c>
       <c r="D104" s="52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E104" s="52">
         <v>6</v>
@@ -10252,7 +10204,7 @@
       <c r="F104" s="52">
         <v>6</v>
       </c>
-      <c r="G104" s="74">
+      <c r="G104" s="52">
         <v>8</v>
       </c>
     </row>
@@ -10264,7 +10216,7 @@
         <v>441</v>
       </c>
       <c r="D105" s="52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E105" s="52">
         <v>7</v>
@@ -10272,7 +10224,7 @@
       <c r="F105" s="52">
         <v>7</v>
       </c>
-      <c r="G105" s="74">
+      <c r="G105" s="52">
         <v>7</v>
       </c>
     </row>
@@ -10284,7 +10236,7 @@
         <v>445</v>
       </c>
       <c r="D106" s="52">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E106" s="52">
         <v>8</v>
@@ -10292,7 +10244,7 @@
       <c r="F106" s="52">
         <v>8</v>
       </c>
-      <c r="G106" s="74">
+      <c r="G106" s="52">
         <v>6</v>
       </c>
     </row>
@@ -10304,7 +10256,7 @@
         <v>445</v>
       </c>
       <c r="D107" s="52">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E107" s="52">
         <v>9</v>
@@ -10312,7 +10264,7 @@
       <c r="F107" s="52">
         <v>9</v>
       </c>
-      <c r="G107" s="74">
+      <c r="G107" s="52">
         <v>10</v>
       </c>
     </row>
@@ -10324,7 +10276,7 @@
         <v>445</v>
       </c>
       <c r="D108" s="52">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E108" s="52">
         <v>10</v>
@@ -10332,7 +10284,7 @@
       <c r="F108" s="52">
         <v>10</v>
       </c>
-      <c r="G108" s="74">
+      <c r="G108" s="52">
         <v>2</v>
       </c>
     </row>
@@ -10344,7 +10296,7 @@
         <v>452</v>
       </c>
       <c r="D109" s="52">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E109" s="52">
         <v>2</v>
@@ -10352,7 +10304,7 @@
       <c r="F109" s="52">
         <v>2</v>
       </c>
-      <c r="G109" s="74">
+      <c r="G109" s="52">
         <v>9</v>
       </c>
     </row>
@@ -10364,7 +10316,7 @@
         <v>453</v>
       </c>
       <c r="D110" s="52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E110" s="52">
         <v>4</v>
@@ -10372,7 +10324,7 @@
       <c r="F110" s="52">
         <v>4</v>
       </c>
-      <c r="G110" s="74">
+      <c r="G110" s="52">
         <v>5</v>
       </c>
     </row>
@@ -10384,7 +10336,7 @@
         <v>454</v>
       </c>
       <c r="D111" s="52">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E111" s="52">
         <v>6</v>
@@ -10392,7 +10344,7 @@
       <c r="F111" s="52">
         <v>6</v>
       </c>
-      <c r="G111" s="74">
+      <c r="G111" s="52">
         <v>1</v>
       </c>
     </row>
@@ -10400,13 +10352,13 @@
     <row r="113" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="114" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="49" t="s">
-        <v>535</v>
-      </c>
-      <c r="B114" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="B114" s="62" t="s">
         <v>300</v>
       </c>
       <c r="E114" s="49" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10427,35 +10379,35 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="69" t="s">
-        <v>550</v>
-      </c>
-      <c r="C116" s="70"/>
-      <c r="D116" s="70"/>
-      <c r="E116" s="70"/>
-      <c r="F116" s="70"/>
+      <c r="B116" s="75" t="s">
+        <v>538</v>
+      </c>
+      <c r="C116" s="76"/>
+      <c r="D116" s="76"/>
+      <c r="E116" s="76"/>
+      <c r="F116" s="76"/>
     </row>
     <row r="117" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="71"/>
-      <c r="C117" s="71"/>
-      <c r="D117" s="71"/>
-      <c r="E117" s="71"/>
-      <c r="F117" s="71"/>
+      <c r="B117" s="73"/>
+      <c r="C117" s="73"/>
+      <c r="D117" s="73"/>
+      <c r="E117" s="73"/>
+      <c r="F117" s="73"/>
     </row>
     <row r="118" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="71"/>
-      <c r="C118" s="71"/>
-      <c r="D118" s="71"/>
-      <c r="E118" s="71"/>
-      <c r="F118" s="71"/>
+      <c r="B118" s="73"/>
+      <c r="C118" s="73"/>
+      <c r="D118" s="73"/>
+      <c r="E118" s="73"/>
+      <c r="F118" s="73"/>
     </row>
     <row r="119" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B121" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="B121" s="62" t="s">
         <v>278</v>
       </c>
     </row>
@@ -10480,7 +10432,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="52" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10496,16 +10448,16 @@
         <v>4</v>
       </c>
       <c r="C126" s="52" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="129" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B129" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="B129" s="62" t="s">
         <v>282</v>
       </c>
     </row>
@@ -10514,39 +10466,43 @@
         <v>283</v>
       </c>
       <c r="C130" s="41" t="s">
-        <v>284</v>
+        <v>560</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="66" t="s">
-        <v>461</v>
-      </c>
-      <c r="C131" s="67"/>
-      <c r="D131" s="68"/>
+      <c r="B131" s="52">
+        <v>1</v>
+      </c>
+      <c r="C131" s="52">
+        <v>1</v>
+      </c>
+      <c r="D131" s="52">
+        <v>2</v>
+      </c>
     </row>
     <row r="132" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="52">
         <v>1</v>
       </c>
       <c r="C132" s="52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D132" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D133" s="52">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10554,7 +10510,7 @@
         <v>2</v>
       </c>
       <c r="C134" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D134" s="52">
         <v>2</v>
@@ -10562,13 +10518,13 @@
     </row>
     <row r="135" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135" s="52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D135" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10576,7 +10532,7 @@
         <v>3</v>
       </c>
       <c r="C136" s="52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D136" s="52">
         <v>4</v>
@@ -10584,13 +10540,13 @@
     </row>
     <row r="137" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B137" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C137" s="52">
+        <v>8</v>
+      </c>
+      <c r="D137" s="52">
         <v>2</v>
-      </c>
-      <c r="D137" s="52">
-        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10598,21 +10554,21 @@
         <v>4</v>
       </c>
       <c r="C138" s="52">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D138" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C139" s="52">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="D139" s="52">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10620,10 +10576,10 @@
         <v>5</v>
       </c>
       <c r="C140" s="52">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="D140" s="52">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10631,10 +10587,10 @@
         <v>5</v>
       </c>
       <c r="C141" s="52">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D141" s="52">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10642,7 +10598,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="52">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D142" s="52">
         <v>1</v>
@@ -10650,10 +10606,10 @@
     </row>
     <row r="143" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C143" s="52">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D143" s="52">
         <v>1</v>
@@ -10661,24 +10617,24 @@
     </row>
     <row r="144" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C144" s="52">
+        <v>1</v>
+      </c>
+      <c r="D144" s="52">
         <v>2</v>
-      </c>
-      <c r="D144" s="52">
-        <v>1</v>
       </c>
     </row>
     <row r="145" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C145" s="52">
+        <v>27</v>
+      </c>
+      <c r="D145" s="52">
         <v>1</v>
-      </c>
-      <c r="D145" s="52">
-        <v>2</v>
       </c>
     </row>
     <row r="146" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10686,7 +10642,7 @@
         <v>8</v>
       </c>
       <c r="C146" s="52">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D146" s="52">
         <v>1</v>
@@ -10697,21 +10653,21 @@
         <v>8</v>
       </c>
       <c r="C147" s="52">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="D147" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C148" s="52">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D148" s="52">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10719,10 +10675,10 @@
         <v>9</v>
       </c>
       <c r="C149" s="52">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="D149" s="52">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10730,10 +10686,10 @@
         <v>9</v>
       </c>
       <c r="C150" s="52">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D150" s="52">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10741,7 +10697,7 @@
         <v>9</v>
       </c>
       <c r="C151" s="52">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D151" s="52">
         <v>2</v>
@@ -10752,21 +10708,21 @@
         <v>9</v>
       </c>
       <c r="C152" s="52">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D152" s="52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B153" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C153" s="52">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D153" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10774,21 +10730,21 @@
         <v>10</v>
       </c>
       <c r="C154" s="52">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D154" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B155" s="52">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C155" s="52">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D155" s="52">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10796,10 +10752,10 @@
         <v>11</v>
       </c>
       <c r="C156" s="52">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D156" s="52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10807,7 +10763,7 @@
         <v>11</v>
       </c>
       <c r="C157" s="52">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D157" s="52">
         <v>1</v>
@@ -10818,10 +10774,10 @@
         <v>11</v>
       </c>
       <c r="C158" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10829,10 +10785,10 @@
         <v>11</v>
       </c>
       <c r="C159" s="52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D159" s="52">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10840,29 +10796,29 @@
         <v>11</v>
       </c>
       <c r="C160" s="52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D160" s="52">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B161" s="52">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C161" s="52">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="D161" s="52">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="52">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C162" s="52">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="D162" s="52">
         <v>1</v>
@@ -10873,119 +10829,120 @@
         <v>13</v>
       </c>
       <c r="C163" s="52">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="D163" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="B166" s="62" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="52">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="52">
-        <v>13</v>
-      </c>
-      <c r="C164" s="52">
-        <v>14</v>
-      </c>
-      <c r="D164" s="52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B167" s="48" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>289</v>
+      <c r="C168" s="52" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B169" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C169" s="52" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B170" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C170" s="52" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B171" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C171" s="52" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B172" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C172" s="52" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B173" s="52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C173" s="52" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" s="52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C174" s="52" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="49" t="s">
+        <v>523</v>
+      </c>
+      <c r="B177" s="62" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="C178" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="D178" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="57" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="52">
-        <v>7</v>
-      </c>
-      <c r="C175" s="52" t="s">
+      <c r="C179" s="49"/>
+      <c r="D179" s="49" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="49" t="s">
-        <v>535</v>
-      </c>
-      <c r="B178" s="48" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="C179" s="41" t="s">
-        <v>294</v>
-      </c>
-      <c r="D179" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>296</v>
+      <c r="E179" s="44" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -10996,20 +10953,20 @@
       <c r="D180" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="E180" s="44" t="s">
-        <v>552</v>
+      <c r="E180" s="58" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="181" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B181" s="57" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C181" s="49"/>
       <c r="D181" s="49" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E181" s="58" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="182" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -11021,389 +10978,403 @@
         <v>475</v>
       </c>
       <c r="E182" s="58" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B183" s="57" t="s">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="C183" s="49"/>
       <c r="D183" s="49" t="s">
-        <v>477</v>
-      </c>
-      <c r="E183" s="58" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="C184" s="49"/>
-      <c r="D184" s="49" t="s">
-        <v>478</v>
-      </c>
-      <c r="E184" s="49"/>
-    </row>
+        <v>476</v>
+      </c>
+      <c r="E183" s="49"/>
+    </row>
+    <row r="184" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="185" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="186" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="B187" s="62" t="s">
+        <v>306</v>
+      </c>
+    </row>
     <row r="188" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B188" s="48" t="s">
-        <v>306</v>
+      <c r="B188" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J188" s="62" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="189" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H189" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J189" s="62" t="s">
-        <v>322</v>
+      <c r="B189" s="52">
+        <v>1</v>
+      </c>
+      <c r="C189" s="52" t="s">
+        <v>549</v>
+      </c>
+      <c r="D189" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="E189" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="F189" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G189" s="59" t="s">
+        <v>479</v>
+      </c>
+      <c r="H189" s="52" t="s">
+        <v>478</v>
+      </c>
+      <c r="J189" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="K189" s="11" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="190" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C190" s="52" t="s">
-        <v>479</v>
-      </c>
-      <c r="D190" s="56" t="s">
+        <v>550</v>
+      </c>
+      <c r="D190" s="52" t="s">
         <v>480</v>
       </c>
       <c r="E190" s="52" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F190" s="52">
         <v>123456789</v>
       </c>
       <c r="G190" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H190" s="52" t="s">
         <v>481</v>
       </c>
-      <c r="J190" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="K190" s="11" t="s">
-        <v>324</v>
+      <c r="J190" s="52">
+        <v>1</v>
+      </c>
+      <c r="K190" s="52" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="191" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C191" s="52" t="s">
-        <v>483</v>
+        <v>551</v>
       </c>
       <c r="D191" s="52" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E191" s="52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F191" s="52">
         <v>123456789</v>
       </c>
       <c r="G191" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H191" s="52" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J191" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K191" s="52" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C192" s="52" t="s">
-        <v>486</v>
+        <v>552</v>
       </c>
       <c r="D192" s="52" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E192" s="52" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F192" s="52">
         <v>123456789</v>
       </c>
       <c r="G192" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H192" s="52" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J192" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K192" s="52" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="193" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C193" s="52" t="s">
-        <v>489</v>
+        <v>553</v>
       </c>
       <c r="D193" s="52" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E193" s="52" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F193" s="52">
         <v>123456789</v>
       </c>
       <c r="G193" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H193" s="52" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J193" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K193" s="52" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="194" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C194" s="52" t="s">
-        <v>492</v>
+        <v>554</v>
       </c>
       <c r="D194" s="52" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E194" s="52" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F194" s="52">
         <v>123456789</v>
       </c>
       <c r="G194" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H194" s="52" t="s">
-        <v>494</v>
-      </c>
-      <c r="J194" s="52">
-        <v>4</v>
-      </c>
-      <c r="K194" s="52" t="s">
-        <v>529</v>
+        <v>489</v>
       </c>
     </row>
     <row r="195" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C195" s="52" t="s">
-        <v>495</v>
+        <v>555</v>
       </c>
       <c r="D195" s="52" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E195" s="52" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F195" s="52">
         <v>123456789</v>
       </c>
       <c r="G195" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H195" s="52" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="196" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C196" s="52" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="D196" s="52" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E196" s="52" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F196" s="52">
         <v>123456789</v>
       </c>
       <c r="G196" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H196" s="52" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="197" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C197" s="52" t="s">
-        <v>501</v>
+        <v>557</v>
       </c>
       <c r="D197" s="52" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="E197" s="52" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F197" s="52">
         <v>123456789</v>
       </c>
       <c r="G197" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H197" s="52" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="198" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B198" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C198" s="52" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="D198" s="52" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E198" s="52" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F198" s="52">
         <v>123456789</v>
       </c>
       <c r="G198" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H198" s="52" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="199" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="52">
-        <v>10</v>
-      </c>
-      <c r="C199" s="52" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I200" s="49" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="201" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B201" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="I201" s="61" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="202" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I202" s="40" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B203" s="52">
+        <v>1</v>
+      </c>
+      <c r="C203" s="52" t="s">
+        <v>468</v>
+      </c>
+      <c r="D203" s="56" t="s">
+        <v>535</v>
+      </c>
+      <c r="E203" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="F203" s="52">
+        <v>123456789</v>
+      </c>
+      <c r="G203" s="59" t="s">
+        <v>479</v>
+      </c>
+      <c r="H203" s="52" t="s">
         <v>507</v>
       </c>
-      <c r="D199" s="52" t="s">
-        <v>508</v>
-      </c>
-      <c r="E199" s="52" t="s">
-        <v>451</v>
-      </c>
-      <c r="F199" s="52">
-        <v>123456789</v>
-      </c>
-      <c r="G199" s="59" t="s">
-        <v>482</v>
-      </c>
-      <c r="H199" s="52" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="200" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I201" s="49" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="202" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="62" t="s">
-        <v>314</v>
-      </c>
-      <c r="I202" s="61" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="203" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G203" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="I203" s="40" t="s">
-        <v>325</v>
+      <c r="I203" s="52">
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B204" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C204" s="52" t="s">
-        <v>470</v>
-      </c>
-      <c r="D204" s="56" t="s">
-        <v>547</v>
+        <v>506</v>
+      </c>
+      <c r="D204" s="49" t="s">
+        <v>536</v>
       </c>
       <c r="E204" s="52" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F204" s="52">
         <v>123456789</v>
       </c>
       <c r="G204" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H204" s="52" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="I204" s="52">
         <v>1</v>
@@ -11411,77 +11382,77 @@
     </row>
     <row r="205" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B205" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C205" s="52" t="s">
-        <v>518</v>
-      </c>
-      <c r="D205" s="49" t="s">
-        <v>548</v>
+        <v>505</v>
+      </c>
+      <c r="D205" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="E205" s="52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F205" s="52">
         <v>123456789</v>
       </c>
       <c r="G205" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H205" s="52" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="I205" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C206" s="52" t="s">
-        <v>517</v>
-      </c>
-      <c r="D206" s="56" t="s">
-        <v>547</v>
+        <v>504</v>
+      </c>
+      <c r="D206" s="49" t="s">
+        <v>536</v>
       </c>
       <c r="E206" s="52" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F206" s="52">
         <v>123456789</v>
       </c>
       <c r="G206" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H206" s="52" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="I206" s="52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C207" s="52" t="s">
-        <v>516</v>
-      </c>
-      <c r="D207" s="49" t="s">
-        <v>548</v>
+        <v>503</v>
+      </c>
+      <c r="D207" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="E207" s="52" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F207" s="52">
         <v>123456789</v>
       </c>
       <c r="G207" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H207" s="52" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="I207" s="52">
         <v>1</v>
@@ -11489,25 +11460,25 @@
     </row>
     <row r="208" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B208" s="52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C208" s="52" t="s">
-        <v>515</v>
-      </c>
-      <c r="D208" s="56" t="s">
-        <v>547</v>
+        <v>502</v>
+      </c>
+      <c r="D208" s="49" t="s">
+        <v>536</v>
       </c>
       <c r="E208" s="52" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F208" s="52">
         <v>123456789</v>
       </c>
       <c r="G208" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H208" s="52" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="I208" s="52">
         <v>1</v>
@@ -11515,315 +11486,300 @@
     </row>
     <row r="209" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B209" s="52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C209" s="52" t="s">
-        <v>514</v>
-      </c>
-      <c r="D209" s="49" t="s">
-        <v>548</v>
+        <v>501</v>
+      </c>
+      <c r="D209" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="E209" s="52" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F209" s="52">
         <v>123456789</v>
       </c>
       <c r="G209" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H209" s="52" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="I209" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B210" s="52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C210" s="52" t="s">
-        <v>513</v>
-      </c>
-      <c r="D210" s="56" t="s">
-        <v>547</v>
+        <v>500</v>
+      </c>
+      <c r="D210" s="49" t="s">
+        <v>536</v>
       </c>
       <c r="E210" s="52" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F210" s="52">
         <v>123456789</v>
       </c>
       <c r="G210" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H210" s="52" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="I210" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B211" s="52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C211" s="52" t="s">
-        <v>512</v>
-      </c>
-      <c r="D211" s="49" t="s">
-        <v>548</v>
+        <v>499</v>
+      </c>
+      <c r="D211" s="56" t="s">
+        <v>535</v>
       </c>
       <c r="E211" s="52" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F211" s="52">
         <v>123456789</v>
       </c>
       <c r="G211" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H211" s="52" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="I211" s="52">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B212" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C212" s="52" t="s">
-        <v>511</v>
-      </c>
-      <c r="D212" s="56" t="s">
-        <v>547</v>
+        <v>498</v>
+      </c>
+      <c r="D212" s="49" t="s">
+        <v>536</v>
       </c>
       <c r="E212" s="52" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F212" s="52">
         <v>123456789</v>
       </c>
       <c r="G212" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H212" s="52" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="I212" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="49" t="s">
+        <v>523</v>
+      </c>
+      <c r="B215" s="62" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B216" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C216" s="40" t="s">
+        <v>328</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="69" t="s">
+        <v>542</v>
+      </c>
+      <c r="C217" s="70"/>
+      <c r="D217" s="70"/>
+      <c r="E217" s="70"/>
+      <c r="F217" s="70"/>
+    </row>
+    <row r="218" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="71"/>
+      <c r="C218" s="71"/>
+      <c r="D218" s="71"/>
+      <c r="E218" s="71"/>
+      <c r="F218" s="71"/>
+    </row>
+    <row r="219" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="71"/>
+      <c r="C219" s="71"/>
+      <c r="D219" s="71"/>
+      <c r="E219" s="71"/>
+      <c r="F219" s="71"/>
+    </row>
+    <row r="220" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="B222" s="62" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B224" s="66" t="s">
+        <v>543</v>
+      </c>
+      <c r="C224" s="67"/>
+      <c r="D224" s="67"/>
+      <c r="E224" s="67"/>
+      <c r="F224" s="67"/>
+      <c r="G224" s="67"/>
+    </row>
+    <row r="225" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" s="68"/>
+      <c r="C225" s="68"/>
+      <c r="D225" s="68"/>
+      <c r="E225" s="68"/>
+      <c r="F225" s="68"/>
+      <c r="G225" s="68"/>
+    </row>
+    <row r="226" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="B228" s="60" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B229" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C229" s="38" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" s="52">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B213" s="52">
-        <v>10</v>
-      </c>
-      <c r="C213" s="52" t="s">
-        <v>510</v>
-      </c>
-      <c r="D213" s="49" t="s">
-        <v>548</v>
-      </c>
-      <c r="E213" s="52" t="s">
-        <v>451</v>
-      </c>
-      <c r="F213" s="52">
-        <v>123456789</v>
-      </c>
-      <c r="G213" s="59" t="s">
-        <v>482</v>
-      </c>
-      <c r="H213" s="52" t="s">
-        <v>528</v>
-      </c>
-      <c r="I213" s="52">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B216" s="48" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="C217" s="40" t="s">
-        <v>328</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="75" t="s">
-        <v>554</v>
-      </c>
-      <c r="C218" s="76"/>
-      <c r="D218" s="76"/>
-      <c r="E218" s="76"/>
-      <c r="F218" s="76"/>
-    </row>
-    <row r="219" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="77"/>
-      <c r="C219" s="77"/>
-      <c r="D219" s="77"/>
-      <c r="E219" s="77"/>
-      <c r="F219" s="77"/>
-    </row>
-    <row r="220" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="77"/>
-      <c r="C220" s="77"/>
-      <c r="D220" s="77"/>
-      <c r="E220" s="77"/>
-      <c r="F220" s="77"/>
-    </row>
-    <row r="221" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B223" s="48" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B224" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B225" s="80" t="s">
-        <v>555</v>
-      </c>
-      <c r="C225" s="79"/>
-      <c r="D225" s="79"/>
-      <c r="E225" s="79"/>
-      <c r="F225" s="79"/>
-      <c r="G225" s="79"/>
-    </row>
-    <row r="226" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B226" s="78"/>
-      <c r="C226" s="78"/>
-      <c r="D226" s="78"/>
-      <c r="E226" s="78"/>
-      <c r="F226" s="78"/>
-      <c r="G226" s="78"/>
-    </row>
-    <row r="227" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B229" s="60" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B230" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="C230" s="38" t="s">
-        <v>341</v>
+      <c r="C230" s="52" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C231" s="52" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
     </row>
     <row r="232" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C232" s="52" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C233" s="52" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B234" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B235" s="52">
-        <v>5</v>
-      </c>
-      <c r="C235" s="52" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="B236" s="48" t="s">
+        <v>342</v>
+      </c>
+    </row>
     <row r="237" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="49" t="s">
-        <v>534</v>
-      </c>
-      <c r="B237" s="48" t="s">
-        <v>342</v>
+      <c r="B237" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="C237" s="41" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B238" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="C238" s="41" t="s">
-        <v>374</v>
+      <c r="B238" s="52">
+        <v>1</v>
+      </c>
+      <c r="C238" s="52">
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C239" s="52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B240" s="52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C240" s="52">
         <v>2</v>
@@ -11831,15 +11787,15 @@
     </row>
     <row r="241" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B241" s="52">
+        <v>4</v>
+      </c>
+      <c r="C241" s="52">
         <v>3</v>
-      </c>
-      <c r="C241" s="52">
-        <v>2</v>
       </c>
     </row>
     <row r="242" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B242" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C242" s="52">
         <v>3</v>
@@ -11847,15 +11803,15 @@
     </row>
     <row r="243" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B243" s="52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C243" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B244" s="52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C244" s="52">
         <v>4</v>
@@ -11863,15 +11819,15 @@
     </row>
     <row r="245" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B245" s="52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C245" s="52">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B246" s="52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C246" s="52">
         <v>5</v>
@@ -11879,20 +11835,13 @@
     </row>
     <row r="247" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B247" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C247" s="52">
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B248" s="52">
-        <v>10</v>
-      </c>
-      <c r="C248" s="52">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="248" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="249" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="250" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="251" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12644,12 +12593,10 @@
     <row r="997" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B225:G226"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="B218:F220"/>
+  <mergeCells count="7">
+    <mergeCell ref="B224:G225"/>
+    <mergeCell ref="B217:F219"/>
     <mergeCell ref="C43:F46"/>
     <mergeCell ref="C51:C60"/>
     <mergeCell ref="C65:F68"/>
